--- a/research/traditional_assets/database/data/finland/finland_real_estate_general_diversified.xlsx
+++ b/research/traditional_assets/database/data/finland/finland_real_estate_general_diversified.xlsx
@@ -1260,7 +1260,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1397,22 +1397,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07143127575127353</v>
+        <v>0.07132441319977098</v>
       </c>
       <c r="C2">
-        <v>141.6574692609801</v>
+        <v>140.5373157810795</v>
       </c>
       <c r="D2">
-        <v>132.8974692609801</v>
+        <v>133.2703157810795</v>
       </c>
       <c r="E2">
-        <v>-88.09999999999999</v>
+        <v>-86.607</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.493</v>
       </c>
       <c r="G2">
         <v>8.76</v>
@@ -1433,28 +1433,28 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0750979</v>
       </c>
       <c r="N2">
-        <v>10.57166666666667</v>
+        <v>10.49656876666667</v>
       </c>
       <c r="O2">
-        <v>2.114333333333334</v>
+        <v>2.099313753333333</v>
       </c>
       <c r="P2">
-        <v>8.457333333333334</v>
+        <v>8.397255013333334</v>
       </c>
       <c r="Q2">
-        <v>8.602333333333334</v>
+        <v>8.542255013333333</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07143127575127353</v>
+        <v>0.07163839717148585</v>
       </c>
       <c r="T2">
-        <v>0.5270060068313374</v>
+        <v>0.5312646412299744</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>140.7718014307546</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1479,22 +1479,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07132441319977098</v>
+        <v>0.07121755064826843</v>
       </c>
       <c r="C3">
-        <v>140.5373157810795</v>
+        <v>139.4192602438053</v>
       </c>
       <c r="D3">
-        <v>133.2703157810795</v>
+        <v>133.6452602438053</v>
       </c>
       <c r="E3">
-        <v>-86.607</v>
+        <v>-85.11399999999999</v>
       </c>
       <c r="F3">
-        <v>1.493</v>
+        <v>2.986</v>
       </c>
       <c r="G3">
         <v>8.76</v>
@@ -1515,28 +1515,28 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M3">
-        <v>0.0750979</v>
+        <v>0.1501958</v>
       </c>
       <c r="N3">
-        <v>10.49656876666667</v>
+        <v>10.42147086666667</v>
       </c>
       <c r="O3">
-        <v>2.099313753333333</v>
+        <v>2.084294173333333</v>
       </c>
       <c r="P3">
-        <v>8.397255013333334</v>
+        <v>8.337176693333333</v>
       </c>
       <c r="Q3">
-        <v>8.542255013333333</v>
+        <v>8.482176693333333</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07163839717148585</v>
+        <v>0.07184974555945758</v>
       </c>
       <c r="T3">
-        <v>0.5312646412299744</v>
+        <v>0.5356101865347062</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>140.7718014307546</v>
+        <v>70.3859007153773</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07121755064826843</v>
+        <v>0.07111068809676589</v>
       </c>
       <c r="C4">
-        <v>139.4192602438053</v>
+        <v>138.3033204062539</v>
       </c>
       <c r="D4">
-        <v>133.6452602438053</v>
+        <v>134.0223204062539</v>
       </c>
       <c r="E4">
-        <v>-85.11399999999999</v>
+        <v>-83.621</v>
       </c>
       <c r="F4">
-        <v>2.986</v>
+        <v>4.479</v>
       </c>
       <c r="G4">
         <v>8.76</v>
@@ -1597,28 +1597,28 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M4">
-        <v>0.1501958</v>
+        <v>0.2252937</v>
       </c>
       <c r="N4">
-        <v>10.42147086666667</v>
+        <v>10.34637296666667</v>
       </c>
       <c r="O4">
-        <v>2.084294173333333</v>
+        <v>2.069274593333334</v>
       </c>
       <c r="P4">
-        <v>8.337176693333333</v>
+        <v>8.277098373333335</v>
       </c>
       <c r="Q4">
-        <v>8.482176693333333</v>
+        <v>8.422098373333334</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07184974555945758</v>
+        <v>0.0720654516461504</v>
       </c>
       <c r="T4">
-        <v>0.5356101865347062</v>
+        <v>0.5400453307117002</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>70.3859007153773</v>
+        <v>46.92393381025154</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1643,22 +1643,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07111068809676589</v>
+        <v>0.07100382554526334</v>
       </c>
       <c r="C5">
-        <v>138.3033204062539</v>
+        <v>137.1895142264846</v>
       </c>
       <c r="D5">
-        <v>134.0223204062539</v>
+        <v>134.4015142264846</v>
       </c>
       <c r="E5">
-        <v>-83.621</v>
+        <v>-82.128</v>
       </c>
       <c r="F5">
-        <v>4.479</v>
+        <v>5.972</v>
       </c>
       <c r="G5">
         <v>8.76</v>
@@ -1679,28 +1679,28 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M5">
-        <v>0.2252937</v>
+        <v>0.3003916</v>
       </c>
       <c r="N5">
-        <v>10.34637296666667</v>
+        <v>10.27127506666667</v>
       </c>
       <c r="O5">
-        <v>2.069274593333334</v>
+        <v>2.054255013333333</v>
       </c>
       <c r="P5">
-        <v>8.277098373333335</v>
+        <v>8.217020053333334</v>
       </c>
       <c r="Q5">
-        <v>8.422098373333334</v>
+        <v>8.362020053333334</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.0720654516461504</v>
+        <v>0.07228565160964931</v>
       </c>
       <c r="T5">
-        <v>0.5400453307117002</v>
+        <v>0.5445728737257153</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>46.92393381025154</v>
+        <v>35.19295035768866</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1725,22 +1725,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07100382554526334</v>
+        <v>0.0708969629937608</v>
       </c>
       <c r="C6">
-        <v>137.1895142264846</v>
+        <v>136.0778598663707</v>
       </c>
       <c r="D6">
-        <v>134.4015142264846</v>
+        <v>134.7828598663707</v>
       </c>
       <c r="E6">
-        <v>-82.128</v>
+        <v>-80.63499999999999</v>
       </c>
       <c r="F6">
-        <v>5.972</v>
+        <v>7.465000000000001</v>
       </c>
       <c r="G6">
         <v>8.76</v>
@@ -1761,28 +1761,28 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M6">
-        <v>0.3003916</v>
+        <v>0.3754895</v>
       </c>
       <c r="N6">
-        <v>10.27127506666667</v>
+        <v>10.19617716666667</v>
       </c>
       <c r="O6">
-        <v>2.054255013333333</v>
+        <v>2.039235433333333</v>
       </c>
       <c r="P6">
-        <v>8.217020053333334</v>
+        <v>8.156941733333333</v>
       </c>
       <c r="Q6">
-        <v>8.362020053333334</v>
+        <v>8.301941733333333</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07228565160964931</v>
+        <v>0.07251048736185348</v>
       </c>
       <c r="T6">
-        <v>0.5445728737257153</v>
+        <v>0.549195733434762</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>35.19295035768866</v>
+        <v>28.15436028615092</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1807,22 +1807,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0708969629937608</v>
+        <v>0.07079010044225825</v>
       </c>
       <c r="C7">
-        <v>136.0778598663707</v>
+        <v>134.9683756944993</v>
       </c>
       <c r="D7">
-        <v>134.7828598663707</v>
+        <v>135.1663756944994</v>
       </c>
       <c r="E7">
-        <v>-80.63499999999999</v>
+        <v>-79.142</v>
       </c>
       <c r="F7">
-        <v>7.465000000000001</v>
+        <v>8.958000000000002</v>
       </c>
       <c r="G7">
         <v>8.76</v>
@@ -1843,28 +1843,28 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M7">
-        <v>0.3754895</v>
+        <v>0.4505874000000001</v>
       </c>
       <c r="N7">
-        <v>10.19617716666667</v>
+        <v>10.12107926666667</v>
       </c>
       <c r="O7">
-        <v>2.039235433333333</v>
+        <v>2.024215853333334</v>
       </c>
       <c r="P7">
-        <v>8.156941733333333</v>
+        <v>8.096863413333335</v>
       </c>
       <c r="Q7">
-        <v>8.301941733333333</v>
+        <v>8.241863413333334</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07251048736185348</v>
+        <v>0.07274010685346623</v>
       </c>
       <c r="T7">
-        <v>0.549195733434762</v>
+        <v>0.5539169518610227</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>28.15436028615092</v>
+        <v>23.46196690512577</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1889,22 +1889,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07079010044225825</v>
+        <v>0.0706832378907557</v>
       </c>
       <c r="C8">
-        <v>134.9683756944993</v>
+        <v>133.8610802891205</v>
       </c>
       <c r="D8">
-        <v>135.1663756944994</v>
+        <v>135.5520802891205</v>
       </c>
       <c r="E8">
-        <v>-79.142</v>
+        <v>-77.649</v>
       </c>
       <c r="F8">
-        <v>8.958</v>
+        <v>10.451</v>
       </c>
       <c r="G8">
         <v>8.76</v>
@@ -1925,28 +1925,28 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M8">
-        <v>0.4505874</v>
+        <v>0.5256853</v>
       </c>
       <c r="N8">
-        <v>10.12107926666667</v>
+        <v>10.04598136666667</v>
       </c>
       <c r="O8">
-        <v>2.024215853333334</v>
+        <v>2.009196273333334</v>
       </c>
       <c r="P8">
-        <v>8.096863413333335</v>
+        <v>8.036785093333334</v>
       </c>
       <c r="Q8">
-        <v>8.241863413333334</v>
+        <v>8.181785093333334</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07274010685346623</v>
+        <v>0.07297466439866204</v>
       </c>
       <c r="T8">
-        <v>0.5539169518610227</v>
+        <v>0.5587397018663427</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>23.46196690512577</v>
+        <v>20.11025734725066</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1971,22 +1971,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07068323789075569</v>
+        <v>0.07057637533925316</v>
       </c>
       <c r="C9">
-        <v>133.8610802891206</v>
+        <v>132.7559924411473</v>
       </c>
       <c r="D9">
-        <v>135.5520802891206</v>
+        <v>135.9399924411473</v>
       </c>
       <c r="E9">
-        <v>-77.64899999999999</v>
+        <v>-76.15599999999999</v>
       </c>
       <c r="F9">
-        <v>10.451</v>
+        <v>11.944</v>
       </c>
       <c r="G9">
         <v>8.76</v>
@@ -2007,28 +2007,28 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M9">
-        <v>0.5256853000000001</v>
+        <v>0.6007832</v>
       </c>
       <c r="N9">
-        <v>10.04598136666667</v>
+        <v>9.970883466666667</v>
       </c>
       <c r="O9">
-        <v>2.009196273333334</v>
+        <v>1.994176693333333</v>
       </c>
       <c r="P9">
-        <v>8.036785093333332</v>
+        <v>7.976706773333333</v>
       </c>
       <c r="Q9">
-        <v>8.181785093333332</v>
+        <v>8.121706773333333</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07297466439866204</v>
+        <v>0.07321432102092734</v>
       </c>
       <c r="T9">
-        <v>0.5587397018663427</v>
+        <v>0.5636672942630826</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>20.11025734725065</v>
+        <v>17.59647517884433</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2053,22 +2053,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07057637533925316</v>
+        <v>0.07046951278775061</v>
       </c>
       <c r="C10">
-        <v>132.7559924411473</v>
+        <v>131.6531311572075</v>
       </c>
       <c r="D10">
-        <v>135.9399924411473</v>
+        <v>136.3301311572075</v>
       </c>
       <c r="E10">
-        <v>-76.15599999999999</v>
+        <v>-74.663</v>
       </c>
       <c r="F10">
-        <v>11.944</v>
+        <v>13.437</v>
       </c>
       <c r="G10">
         <v>8.76</v>
@@ -2089,28 +2089,28 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M10">
-        <v>0.6007832</v>
+        <v>0.6758811</v>
       </c>
       <c r="N10">
-        <v>9.970883466666667</v>
+        <v>9.895785566666667</v>
       </c>
       <c r="O10">
-        <v>1.994176693333333</v>
+        <v>1.979157113333334</v>
       </c>
       <c r="P10">
-        <v>7.976706773333333</v>
+        <v>7.916628453333334</v>
       </c>
       <c r="Q10">
-        <v>8.121706773333333</v>
+        <v>8.061628453333334</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07321432102092734</v>
+        <v>0.07345924482170396</v>
       </c>
       <c r="T10">
-        <v>0.5636672942630826</v>
+        <v>0.5687031853938168</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>17.59647517884433</v>
+        <v>15.64131127008385</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2135,22 +2135,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07046951278775061</v>
+        <v>0.07036265023624806</v>
       </c>
       <c r="C11">
-        <v>131.6531311572075</v>
+        <v>130.5525156627479</v>
       </c>
       <c r="D11">
-        <v>136.3301311572075</v>
+        <v>136.7225156627479</v>
       </c>
       <c r="E11">
-        <v>-74.663</v>
+        <v>-73.16999999999999</v>
       </c>
       <c r="F11">
-        <v>13.437</v>
+        <v>14.93</v>
       </c>
       <c r="G11">
         <v>8.76</v>
@@ -2171,28 +2171,28 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M11">
-        <v>0.6758811</v>
+        <v>0.750979</v>
       </c>
       <c r="N11">
-        <v>9.895785566666667</v>
+        <v>9.820687666666668</v>
       </c>
       <c r="O11">
-        <v>1.979157113333334</v>
+        <v>1.964137533333334</v>
       </c>
       <c r="P11">
-        <v>7.916628453333334</v>
+        <v>7.856550133333334</v>
       </c>
       <c r="Q11">
-        <v>8.061628453333334</v>
+        <v>8.001550133333334</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07345924482170396</v>
+        <v>0.07370961137360896</v>
       </c>
       <c r="T11">
-        <v>0.5687031853938168</v>
+        <v>0.573850985216345</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>15.64131127008385</v>
+        <v>14.07718014307546</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2217,22 +2217,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07036265023624806</v>
+        <v>0.07038778768474552</v>
       </c>
       <c r="C12">
-        <v>130.5525156627479</v>
+        <v>128.9670113978927</v>
       </c>
       <c r="D12">
-        <v>136.7225156627479</v>
+        <v>136.6300113978927</v>
       </c>
       <c r="E12">
-        <v>-73.16999999999999</v>
+        <v>-71.67699999999999</v>
       </c>
       <c r="F12">
-        <v>14.93</v>
+        <v>16.423</v>
       </c>
       <c r="G12">
         <v>8.76</v>
@@ -2253,45 +2253,45 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M12">
-        <v>0.7509790000000001</v>
+        <v>0.8507114000000001</v>
       </c>
       <c r="N12">
-        <v>9.820687666666668</v>
+        <v>9.720955266666667</v>
       </c>
       <c r="O12">
-        <v>1.964137533333334</v>
+        <v>1.944191053333334</v>
       </c>
       <c r="P12">
-        <v>7.856550133333334</v>
+        <v>7.776764213333334</v>
       </c>
       <c r="Q12">
-        <v>8.001550133333334</v>
+        <v>7.921764213333334</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07370961137360896</v>
+        <v>0.0739656041401635</v>
       </c>
       <c r="T12">
-        <v>0.5738509852163451</v>
+        <v>0.5791144659337617</v>
       </c>
       <c r="U12">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V12">
         <v>0.2</v>
       </c>
       <c r="W12">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y12">
-        <v>14.07718014307546</v>
+        <v>12.42685435585637</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2299,22 +2299,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07038778768474552</v>
+        <v>0.07029292513324296</v>
       </c>
       <c r="C13">
-        <v>128.9670113978927</v>
+        <v>127.8237565579635</v>
       </c>
       <c r="D13">
-        <v>136.6300113978927</v>
+        <v>136.9797565579636</v>
       </c>
       <c r="E13">
-        <v>-71.67699999999999</v>
+        <v>-70.184</v>
       </c>
       <c r="F13">
-        <v>16.423</v>
+        <v>17.916</v>
       </c>
       <c r="G13">
         <v>8.76</v>
@@ -2335,28 +2335,28 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M13">
-        <v>0.8507114000000001</v>
+        <v>0.9280488</v>
       </c>
       <c r="N13">
-        <v>9.720955266666667</v>
+        <v>9.643617866666666</v>
       </c>
       <c r="O13">
-        <v>1.944191053333334</v>
+        <v>1.928723573333333</v>
       </c>
       <c r="P13">
-        <v>7.776764213333334</v>
+        <v>7.714894293333333</v>
       </c>
       <c r="Q13">
-        <v>7.921764213333334</v>
+        <v>7.859894293333332</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.0739656041401635</v>
+        <v>0.07422741492413973</v>
       </c>
       <c r="T13">
-        <v>0.5791144659337617</v>
+        <v>0.5844975712129378</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>12.42685435585637</v>
+        <v>11.391283159535</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2381,22 +2381,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07029292513324296</v>
+        <v>0.07019806258174041</v>
       </c>
       <c r="C14">
-        <v>127.8237565579635</v>
+        <v>126.6822968668167</v>
       </c>
       <c r="D14">
-        <v>136.9797565579636</v>
+        <v>137.3312968668167</v>
       </c>
       <c r="E14">
-        <v>-70.184</v>
+        <v>-68.69099999999999</v>
       </c>
       <c r="F14">
-        <v>17.916</v>
+        <v>19.409</v>
       </c>
       <c r="G14">
         <v>8.76</v>
@@ -2417,28 +2417,28 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M14">
-        <v>0.9280488</v>
+        <v>1.0053862</v>
       </c>
       <c r="N14">
-        <v>9.643617866666666</v>
+        <v>9.566280466666667</v>
       </c>
       <c r="O14">
-        <v>1.928723573333333</v>
+        <v>1.913256093333334</v>
       </c>
       <c r="P14">
-        <v>7.714894293333333</v>
+        <v>7.653024373333333</v>
       </c>
       <c r="Q14">
-        <v>7.859894293333332</v>
+        <v>7.798024373333333</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07422741492413973</v>
+        <v>0.07449524434682807</v>
       </c>
       <c r="T14">
-        <v>0.5844975712129378</v>
+        <v>0.5900044260387616</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.391283159535</v>
+        <v>10.51503060880154</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2463,22 +2463,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07019806258174041</v>
+        <v>0.07029360003023787</v>
       </c>
       <c r="C15">
-        <v>126.6822968668167</v>
+        <v>124.8352619817188</v>
       </c>
       <c r="D15">
-        <v>137.3312968668167</v>
+        <v>136.9772619817188</v>
       </c>
       <c r="E15">
-        <v>-68.69099999999999</v>
+        <v>-67.19799999999999</v>
       </c>
       <c r="F15">
-        <v>19.409</v>
+        <v>20.902</v>
       </c>
       <c r="G15">
         <v>8.76</v>
@@ -2499,45 +2499,45 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M15">
-        <v>1.0053862</v>
+        <v>1.118257</v>
       </c>
       <c r="N15">
-        <v>9.566280466666667</v>
+        <v>9.453409666666667</v>
       </c>
       <c r="O15">
-        <v>1.913256093333334</v>
+        <v>1.890681933333334</v>
       </c>
       <c r="P15">
-        <v>7.653024373333333</v>
+        <v>7.562727733333334</v>
       </c>
       <c r="Q15">
-        <v>7.798024373333333</v>
+        <v>7.707727733333334</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07449524434682807</v>
+        <v>0.07476930236074171</v>
       </c>
       <c r="T15">
-        <v>0.5900044260387616</v>
+        <v>0.5956393472558836</v>
       </c>
       <c r="U15">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V15">
         <v>0.2</v>
       </c>
       <c r="W15">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>10.51503060880154</v>
+        <v>9.453700416511289</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2545,22 +2545,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07029360003023787</v>
+        <v>0.07021233747873533</v>
       </c>
       <c r="C16">
-        <v>124.8352619817188</v>
+        <v>123.6432818679486</v>
       </c>
       <c r="D16">
-        <v>136.9772619817188</v>
+        <v>137.2782818679486</v>
       </c>
       <c r="E16">
-        <v>-67.19799999999999</v>
+        <v>-65.70499999999998</v>
       </c>
       <c r="F16">
-        <v>20.902</v>
+        <v>22.39500000000001</v>
       </c>
       <c r="G16">
         <v>8.76</v>
@@ -2581,28 +2581,28 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M16">
-        <v>1.118257</v>
+        <v>1.1981325</v>
       </c>
       <c r="N16">
-        <v>9.453409666666667</v>
+        <v>9.373534166666667</v>
       </c>
       <c r="O16">
-        <v>1.890681933333334</v>
+        <v>1.874706833333334</v>
       </c>
       <c r="P16">
-        <v>7.562727733333334</v>
+        <v>7.498827333333334</v>
       </c>
       <c r="Q16">
-        <v>7.707727733333334</v>
+        <v>7.643827333333333</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07476930236074171</v>
+        <v>0.07504980879851215</v>
       </c>
       <c r="T16">
-        <v>0.5956393472558836</v>
+        <v>0.601406854854585</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>9.453700416511289</v>
+        <v>8.823453722077204</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07021233747873533</v>
+        <v>0.07013107492723278</v>
       </c>
       <c r="C17">
-        <v>123.6432818679486</v>
+        <v>122.4526277047682</v>
       </c>
       <c r="D17">
-        <v>137.2782818679486</v>
+        <v>137.5806277047682</v>
       </c>
       <c r="E17">
-        <v>-65.705</v>
+        <v>-64.21199999999999</v>
       </c>
       <c r="F17">
-        <v>22.395</v>
+        <v>23.888</v>
       </c>
       <c r="G17">
         <v>8.76</v>
@@ -2663,28 +2663,28 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M17">
-        <v>1.1981325</v>
+        <v>1.278008</v>
       </c>
       <c r="N17">
-        <v>9.373534166666667</v>
+        <v>9.293658666666667</v>
       </c>
       <c r="O17">
-        <v>1.874706833333334</v>
+        <v>1.858731733333334</v>
       </c>
       <c r="P17">
-        <v>7.498827333333334</v>
+        <v>7.434926933333334</v>
       </c>
       <c r="Q17">
-        <v>7.643827333333333</v>
+        <v>7.579926933333334</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07504980879851215</v>
+        <v>0.0753369939609914</v>
       </c>
       <c r="T17">
-        <v>0.601406854854585</v>
+        <v>0.6073116840627792</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.823453722077204</v>
+        <v>8.271987864447379</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2709,22 +2709,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07013107492723278</v>
+        <v>0.07004981237573023</v>
       </c>
       <c r="C18">
-        <v>122.4526277047682</v>
+        <v>121.2633082724564</v>
       </c>
       <c r="D18">
-        <v>137.5806277047682</v>
+        <v>137.8843082724564</v>
       </c>
       <c r="E18">
-        <v>-64.21199999999999</v>
+        <v>-62.71899999999999</v>
       </c>
       <c r="F18">
-        <v>23.888</v>
+        <v>25.381</v>
       </c>
       <c r="G18">
         <v>8.76</v>
@@ -2745,28 +2745,28 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M18">
-        <v>1.278008</v>
+        <v>1.3578835</v>
       </c>
       <c r="N18">
-        <v>9.293658666666667</v>
+        <v>9.213783166666667</v>
       </c>
       <c r="O18">
-        <v>1.858731733333334</v>
+        <v>1.842756633333334</v>
       </c>
       <c r="P18">
-        <v>7.434926933333334</v>
+        <v>7.371026533333334</v>
       </c>
       <c r="Q18">
-        <v>7.579926933333334</v>
+        <v>7.516026533333333</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.0753369939609914</v>
+        <v>0.07563109924786775</v>
       </c>
       <c r="T18">
-        <v>0.6073116840627792</v>
+        <v>0.6133587983121348</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.271987864447379</v>
+        <v>7.785400343009298</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2791,22 +2791,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07004981237573023</v>
+        <v>0.07008374982422769</v>
       </c>
       <c r="C19">
-        <v>121.2633082724564</v>
+        <v>119.6433201403104</v>
       </c>
       <c r="D19">
-        <v>137.8843082724564</v>
+        <v>137.7573201403104</v>
       </c>
       <c r="E19">
-        <v>-62.71899999999999</v>
+        <v>-61.22599999999998</v>
       </c>
       <c r="F19">
-        <v>25.381</v>
+        <v>26.87400000000001</v>
       </c>
       <c r="G19">
         <v>8.76</v>
@@ -2827,45 +2827,45 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M19">
-        <v>1.3578835</v>
+        <v>1.4592582</v>
       </c>
       <c r="N19">
-        <v>9.213783166666667</v>
+        <v>9.112408466666666</v>
       </c>
       <c r="O19">
-        <v>1.842756633333334</v>
+        <v>1.822481693333333</v>
       </c>
       <c r="P19">
-        <v>7.371026533333334</v>
+        <v>7.289926773333333</v>
       </c>
       <c r="Q19">
-        <v>7.516026533333333</v>
+        <v>7.434926773333332</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07563109924786775</v>
+        <v>0.07593237783442401</v>
       </c>
       <c r="T19">
-        <v>0.6133587983121348</v>
+        <v>0.6195534031529382</v>
       </c>
       <c r="U19">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V19">
         <v>0.2</v>
       </c>
       <c r="W19">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y19">
-        <v>7.785400343009298</v>
+        <v>7.244548405941227</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2873,22 +2873,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0700837498242277</v>
+        <v>0.07000888727272515</v>
       </c>
       <c r="C20">
-        <v>119.6433201403104</v>
+        <v>118.4307547521889</v>
       </c>
       <c r="D20">
-        <v>137.7573201403104</v>
+        <v>138.0377547521889</v>
       </c>
       <c r="E20">
-        <v>-61.22599999999999</v>
+        <v>-59.73299999999999</v>
       </c>
       <c r="F20">
-        <v>26.874</v>
+        <v>28.367</v>
       </c>
       <c r="G20">
         <v>8.76</v>
@@ -2909,28 +2909,28 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M20">
-        <v>1.4592582</v>
+        <v>1.5403281</v>
       </c>
       <c r="N20">
-        <v>9.112408466666666</v>
+        <v>9.031338566666667</v>
       </c>
       <c r="O20">
-        <v>1.822481693333333</v>
+        <v>1.806267713333334</v>
       </c>
       <c r="P20">
-        <v>7.289926773333333</v>
+        <v>7.225070853333333</v>
       </c>
       <c r="Q20">
-        <v>7.434926773333332</v>
+        <v>7.370070853333333</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07593237783442401</v>
+        <v>0.07624109539842611</v>
       </c>
       <c r="T20">
-        <v>0.6195534031529381</v>
+        <v>0.6259009611996872</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.244548405941228</v>
+        <v>6.863256384575902</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2955,22 +2955,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07000888727272515</v>
+        <v>0.06993402472122259</v>
       </c>
       <c r="C21">
-        <v>118.4307547521889</v>
+        <v>117.2193334628917</v>
       </c>
       <c r="D21">
-        <v>138.0377547521889</v>
+        <v>138.3193334628917</v>
       </c>
       <c r="E21">
-        <v>-59.73299999999999</v>
+        <v>-58.23999999999999</v>
       </c>
       <c r="F21">
-        <v>28.367</v>
+        <v>29.86</v>
       </c>
       <c r="G21">
         <v>8.76</v>
@@ -2991,28 +2991,28 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M21">
-        <v>1.5403281</v>
+        <v>1.621398</v>
       </c>
       <c r="N21">
-        <v>9.031338566666667</v>
+        <v>8.950268666666666</v>
       </c>
       <c r="O21">
-        <v>1.806267713333334</v>
+        <v>1.790053733333333</v>
       </c>
       <c r="P21">
-        <v>7.225070853333333</v>
+        <v>7.160214933333333</v>
       </c>
       <c r="Q21">
-        <v>7.370070853333333</v>
+        <v>7.305214933333333</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07624109539842611</v>
+        <v>0.07655753090152824</v>
       </c>
       <c r="T21">
-        <v>0.6259009611996872</v>
+        <v>0.6324072081976048</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3029,7 +3029,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.863256384575902</v>
+        <v>6.520093565347105</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3037,22 +3037,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.06993402472122259</v>
+        <v>0.06985916216972005</v>
       </c>
       <c r="C22">
-        <v>117.2193334628917</v>
+        <v>116.0090632881592</v>
       </c>
       <c r="D22">
-        <v>138.3193334628917</v>
+        <v>138.6020632881592</v>
       </c>
       <c r="E22">
-        <v>-58.23999999999999</v>
+        <v>-56.74699999999999</v>
       </c>
       <c r="F22">
-        <v>29.86</v>
+        <v>31.35300000000001</v>
       </c>
       <c r="G22">
         <v>8.76</v>
@@ -3073,28 +3073,28 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M22">
-        <v>1.621398</v>
+        <v>1.7024679</v>
       </c>
       <c r="N22">
-        <v>8.950268666666666</v>
+        <v>8.869198766666667</v>
       </c>
       <c r="O22">
-        <v>1.790053733333333</v>
+        <v>1.773839753333333</v>
       </c>
       <c r="P22">
-        <v>7.160214933333333</v>
+        <v>7.095359013333334</v>
       </c>
       <c r="Q22">
-        <v>7.305214933333333</v>
+        <v>7.240359013333333</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07655753090152824</v>
+        <v>0.07688197743002537</v>
       </c>
       <c r="T22">
-        <v>0.6324072081976048</v>
+        <v>0.639078170309394</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.520093565347105</v>
+        <v>6.209612919378196</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3119,22 +3119,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06985916216972005</v>
+        <v>0.06996029961821751</v>
       </c>
       <c r="C23">
-        <v>116.0090632881592</v>
+        <v>114.1343755800095</v>
       </c>
       <c r="D23">
-        <v>138.6020632881592</v>
+        <v>138.2203755800095</v>
       </c>
       <c r="E23">
-        <v>-56.74699999999999</v>
+        <v>-55.25399999999999</v>
       </c>
       <c r="F23">
-        <v>31.353</v>
+        <v>32.846</v>
       </c>
       <c r="G23">
         <v>8.76</v>
@@ -3155,45 +3155,45 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M23">
-        <v>1.7024679</v>
+        <v>1.8163838</v>
       </c>
       <c r="N23">
-        <v>8.869198766666667</v>
+        <v>8.755282866666667</v>
       </c>
       <c r="O23">
-        <v>1.773839753333333</v>
+        <v>1.751056573333333</v>
       </c>
       <c r="P23">
-        <v>7.095359013333334</v>
+        <v>7.004226293333334</v>
       </c>
       <c r="Q23">
-        <v>7.240359013333333</v>
+        <v>7.149226293333333</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07688197743002537</v>
+        <v>0.07721474310027884</v>
       </c>
       <c r="T23">
-        <v>0.639078170309394</v>
+        <v>0.6459201827317417</v>
       </c>
       <c r="U23">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V23">
         <v>0.2</v>
       </c>
       <c r="W23">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y23">
-        <v>6.209612919378196</v>
+        <v>5.820172293249183</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3201,22 +3201,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06996029961821751</v>
+        <v>0.06989343706671494</v>
       </c>
       <c r="C24">
-        <v>114.1343755800095</v>
+        <v>112.8934756044273</v>
       </c>
       <c r="D24">
-        <v>138.2203755800095</v>
+        <v>138.4724756044273</v>
       </c>
       <c r="E24">
-        <v>-55.25399999999999</v>
+        <v>-53.76099999999999</v>
       </c>
       <c r="F24">
-        <v>32.846</v>
+        <v>34.33900000000001</v>
       </c>
       <c r="G24">
         <v>8.76</v>
@@ -3237,28 +3237,28 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M24">
-        <v>1.8163838</v>
+        <v>1.8989467</v>
       </c>
       <c r="N24">
-        <v>8.755282866666667</v>
+        <v>8.672719966666667</v>
       </c>
       <c r="O24">
-        <v>1.751056573333333</v>
+        <v>1.734543993333334</v>
       </c>
       <c r="P24">
-        <v>7.004226293333334</v>
+        <v>6.938175973333334</v>
       </c>
       <c r="Q24">
-        <v>7.149226293333333</v>
+        <v>7.083175973333334</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07721474310027884</v>
+        <v>0.07755615203469474</v>
       </c>
       <c r="T24">
-        <v>0.6459201827317417</v>
+        <v>0.6529399097624622</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3275,7 +3275,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.820172293249183</v>
+        <v>5.56712132397748</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3283,22 +3283,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06989343706671494</v>
+        <v>0.06982657451521242</v>
       </c>
       <c r="C25">
-        <v>112.8934756044273</v>
+        <v>111.6534969192221</v>
       </c>
       <c r="D25">
-        <v>138.4724756044273</v>
+        <v>138.7254969192221</v>
       </c>
       <c r="E25">
-        <v>-53.76099999999999</v>
+        <v>-52.26799999999999</v>
       </c>
       <c r="F25">
-        <v>34.33900000000001</v>
+        <v>35.83200000000001</v>
       </c>
       <c r="G25">
         <v>8.76</v>
@@ -3319,28 +3319,28 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M25">
-        <v>1.8989467</v>
+        <v>1.981509600000001</v>
       </c>
       <c r="N25">
-        <v>8.672719966666667</v>
+        <v>8.590157066666666</v>
       </c>
       <c r="O25">
-        <v>1.734543993333334</v>
+        <v>1.718031413333333</v>
       </c>
       <c r="P25">
-        <v>6.938175973333334</v>
+        <v>6.872125653333333</v>
       </c>
       <c r="Q25">
-        <v>7.083175973333334</v>
+        <v>7.017125653333332</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07755615203469474</v>
+        <v>0.07790654541475317</v>
       </c>
       <c r="T25">
-        <v>0.6529399097624622</v>
+        <v>0.6601443664518858</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.56712132397748</v>
+        <v>5.335157935478417</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3365,22 +3365,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.0698265745152124</v>
+        <v>0.06975971196370986</v>
       </c>
       <c r="C26">
-        <v>111.6534969192221</v>
+        <v>110.4144445838723</v>
       </c>
       <c r="D26">
-        <v>138.7254969192221</v>
+        <v>138.9794445838723</v>
       </c>
       <c r="E26">
-        <v>-52.26799999999999</v>
+        <v>-50.77499999999999</v>
       </c>
       <c r="F26">
-        <v>35.832</v>
+        <v>37.325</v>
       </c>
       <c r="G26">
         <v>8.76</v>
@@ -3401,28 +3401,28 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M26">
-        <v>1.9815096</v>
+        <v>2.0640725</v>
       </c>
       <c r="N26">
-        <v>8.590157066666666</v>
+        <v>8.507594166666667</v>
       </c>
       <c r="O26">
-        <v>1.718031413333333</v>
+        <v>1.701518833333334</v>
       </c>
       <c r="P26">
-        <v>6.872125653333333</v>
+        <v>6.806075333333334</v>
       </c>
       <c r="Q26">
-        <v>7.017125653333332</v>
+        <v>6.951075333333334</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07790654541475316</v>
+        <v>0.07826628261827981</v>
       </c>
       <c r="T26">
-        <v>0.6601443664518857</v>
+        <v>0.6675409419863606</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.335157935478418</v>
+        <v>5.121751618059281</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3447,22 +3447,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06975971196370986</v>
+        <v>0.06969284941220731</v>
       </c>
       <c r="C27">
-        <v>110.4144445838723</v>
+        <v>109.1763236949709</v>
       </c>
       <c r="D27">
-        <v>138.9794445838723</v>
+        <v>139.234323694971</v>
       </c>
       <c r="E27">
-        <v>-50.77499999999999</v>
+        <v>-49.28199999999999</v>
       </c>
       <c r="F27">
-        <v>37.325</v>
+        <v>38.818</v>
       </c>
       <c r="G27">
         <v>8.76</v>
@@ -3483,28 +3483,28 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M27">
-        <v>2.0640725</v>
+        <v>2.146635400000001</v>
       </c>
       <c r="N27">
-        <v>8.507594166666667</v>
+        <v>8.425031266666666</v>
       </c>
       <c r="O27">
-        <v>1.701518833333334</v>
+        <v>1.685006253333333</v>
       </c>
       <c r="P27">
-        <v>6.806075333333334</v>
+        <v>6.740025013333333</v>
       </c>
       <c r="Q27">
-        <v>6.951075333333334</v>
+        <v>6.885025013333332</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07826628261827981</v>
+        <v>0.07863574244892879</v>
       </c>
       <c r="T27">
-        <v>0.6675409419863606</v>
+        <v>0.6751374249677132</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.121751618059281</v>
+        <v>4.924761171210847</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3529,22 +3529,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06969284941220731</v>
+        <v>0.06962598686070477</v>
       </c>
       <c r="C28">
-        <v>109.1763236949709</v>
+        <v>107.9391393865671</v>
       </c>
       <c r="D28">
-        <v>139.234323694971</v>
+        <v>139.4901393865671</v>
       </c>
       <c r="E28">
-        <v>-49.28199999999999</v>
+        <v>-47.78899999999999</v>
       </c>
       <c r="F28">
-        <v>38.818</v>
+        <v>40.31100000000001</v>
       </c>
       <c r="G28">
         <v>8.76</v>
@@ -3565,28 +3565,28 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M28">
-        <v>2.146635400000001</v>
+        <v>2.229198300000001</v>
       </c>
       <c r="N28">
-        <v>8.425031266666666</v>
+        <v>8.342468366666667</v>
       </c>
       <c r="O28">
-        <v>1.685006253333333</v>
+        <v>1.668493673333334</v>
       </c>
       <c r="P28">
-        <v>6.740025013333333</v>
+        <v>6.673974693333333</v>
       </c>
       <c r="Q28">
-        <v>6.885025013333332</v>
+        <v>6.818974693333333</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07863574244892879</v>
+        <v>0.07901532446671886</v>
       </c>
       <c r="T28">
-        <v>0.6751374249677132</v>
+        <v>0.6829420307704729</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.924761171210847</v>
+        <v>4.742362609314149</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3611,22 +3611,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.06962598686070477</v>
+        <v>0.06955912430920222</v>
       </c>
       <c r="C29">
-        <v>107.9391393865671</v>
+        <v>106.7028968305105</v>
       </c>
       <c r="D29">
-        <v>139.4901393865671</v>
+        <v>139.7468968305105</v>
       </c>
       <c r="E29">
-        <v>-47.78899999999999</v>
+        <v>-46.29599999999999</v>
       </c>
       <c r="F29">
-        <v>40.31100000000001</v>
+        <v>41.80400000000001</v>
       </c>
       <c r="G29">
         <v>8.76</v>
@@ -3647,28 +3647,28 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M29">
-        <v>2.229198300000001</v>
+        <v>2.311761200000001</v>
       </c>
       <c r="N29">
-        <v>8.342468366666667</v>
+        <v>8.259905466666666</v>
       </c>
       <c r="O29">
-        <v>1.668493673333334</v>
+        <v>1.651981093333333</v>
       </c>
       <c r="P29">
-        <v>6.673974693333333</v>
+        <v>6.607924373333333</v>
       </c>
       <c r="Q29">
-        <v>6.818974693333333</v>
+        <v>6.752924373333332</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07901532446671886</v>
+        <v>0.07940545042944752</v>
       </c>
       <c r="T29">
-        <v>0.6829420307704729</v>
+        <v>0.6909634311788645</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.742362609314149</v>
+        <v>4.572992516124357</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.06955912430920222</v>
+        <v>0.07007226175769968</v>
       </c>
       <c r="C30">
-        <v>106.7028968305105</v>
+        <v>103.2632803255822</v>
       </c>
       <c r="D30">
-        <v>139.7468968305105</v>
+        <v>137.8002803255822</v>
       </c>
       <c r="E30">
-        <v>-46.29599999999999</v>
+        <v>-44.80299999999998</v>
       </c>
       <c r="F30">
-        <v>41.80400000000001</v>
+        <v>43.29700000000001</v>
       </c>
       <c r="G30">
         <v>8.76</v>
@@ -3729,45 +3729,45 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M30">
-        <v>2.311761200000001</v>
+        <v>2.502566600000001</v>
       </c>
       <c r="N30">
-        <v>8.259905466666666</v>
+        <v>8.069100066666667</v>
       </c>
       <c r="O30">
-        <v>1.651981093333333</v>
+        <v>1.613820013333334</v>
       </c>
       <c r="P30">
-        <v>6.607924373333333</v>
+        <v>6.455280053333334</v>
       </c>
       <c r="Q30">
-        <v>6.752924373333332</v>
+        <v>6.600280053333334</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07940545042944752</v>
+        <v>0.07980656585591503</v>
       </c>
       <c r="T30">
-        <v>0.6909634311788645</v>
+        <v>0.6992107865283378</v>
       </c>
       <c r="U30">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V30">
         <v>0.2</v>
       </c>
       <c r="W30">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y30">
-        <v>4.572992516124357</v>
+        <v>4.224329800720055</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3775,22 +3775,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07007226175769968</v>
+        <v>0.07002539920619712</v>
       </c>
       <c r="C31">
-        <v>103.2632803255822</v>
+        <v>101.9458030613082</v>
       </c>
       <c r="D31">
-        <v>137.8002803255822</v>
+        <v>137.9758030613082</v>
       </c>
       <c r="E31">
-        <v>-44.803</v>
+        <v>-43.31</v>
       </c>
       <c r="F31">
-        <v>43.297</v>
+        <v>44.79</v>
       </c>
       <c r="G31">
         <v>8.76</v>
@@ -3811,28 +3811,28 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M31">
-        <v>2.5025666</v>
+        <v>2.588862</v>
       </c>
       <c r="N31">
-        <v>8.069100066666667</v>
+        <v>7.982804666666667</v>
       </c>
       <c r="O31">
-        <v>1.613820013333334</v>
+        <v>1.596560933333333</v>
       </c>
       <c r="P31">
-        <v>6.455280053333334</v>
+        <v>6.386243733333333</v>
       </c>
       <c r="Q31">
-        <v>6.600280053333334</v>
+        <v>6.531243733333333</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.07980656585591503</v>
+        <v>0.08021914172313874</v>
       </c>
       <c r="T31">
-        <v>0.6992107865283378</v>
+        <v>0.7076937806020817</v>
       </c>
       <c r="U31">
         <v>0.0578</v>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.224329800720056</v>
+        <v>4.08351880736272</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3857,22 +3857,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07002539920619712</v>
+        <v>0.07084653665469456</v>
       </c>
       <c r="C32">
-        <v>101.9458030613082</v>
+        <v>97.44056190630023</v>
       </c>
       <c r="D32">
-        <v>137.9758030613082</v>
+        <v>134.9635619063002</v>
       </c>
       <c r="E32">
-        <v>-43.31</v>
+        <v>-41.81699999999999</v>
       </c>
       <c r="F32">
-        <v>44.79</v>
+        <v>46.283</v>
       </c>
       <c r="G32">
         <v>8.76</v>
@@ -3893,45 +3893,45 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M32">
-        <v>2.588862</v>
+        <v>2.8371479</v>
       </c>
       <c r="N32">
-        <v>7.982804666666667</v>
+        <v>7.734518766666667</v>
       </c>
       <c r="O32">
-        <v>1.596560933333333</v>
+        <v>1.546903753333334</v>
       </c>
       <c r="P32">
-        <v>6.386243733333333</v>
+        <v>6.187615013333334</v>
       </c>
       <c r="Q32">
-        <v>6.531243733333333</v>
+        <v>6.332615013333333</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08021914172313874</v>
+        <v>0.08064367631115155</v>
       </c>
       <c r="T32">
-        <v>0.7076937806020817</v>
+        <v>0.7164226585620209</v>
       </c>
       <c r="U32">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V32">
         <v>0.2</v>
       </c>
       <c r="W32">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y32">
-        <v>4.08351880736272</v>
+        <v>3.726159875791695</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3939,22 +3939,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07084653665469456</v>
+        <v>0.07082767410319202</v>
       </c>
       <c r="C33">
-        <v>97.44056190630023</v>
+        <v>96.01528016342493</v>
       </c>
       <c r="D33">
-        <v>134.9635619063002</v>
+        <v>135.031280163425</v>
       </c>
       <c r="E33">
-        <v>-41.81699999999999</v>
+        <v>-40.32399999999999</v>
       </c>
       <c r="F33">
-        <v>46.283</v>
+        <v>47.776</v>
       </c>
       <c r="G33">
         <v>8.76</v>
@@ -3975,28 +3975,28 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M33">
-        <v>2.8371479</v>
+        <v>2.9286688</v>
       </c>
       <c r="N33">
-        <v>7.734518766666667</v>
+        <v>7.642997866666667</v>
       </c>
       <c r="O33">
-        <v>1.546903753333334</v>
+        <v>1.528599573333334</v>
       </c>
       <c r="P33">
-        <v>6.187615013333334</v>
+        <v>6.114398293333333</v>
       </c>
       <c r="Q33">
-        <v>6.332615013333333</v>
+        <v>6.259398293333333</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08064367631115155</v>
+        <v>0.08108069721057651</v>
       </c>
       <c r="T33">
-        <v>0.7164226585620209</v>
+        <v>0.7254082682266644</v>
       </c>
       <c r="U33">
         <v>0.0613</v>
@@ -4013,7 +4013,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.726159875791695</v>
+        <v>3.609717379673204</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4021,22 +4021,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07082767410319202</v>
+        <v>0.07080881155168947</v>
       </c>
       <c r="C34">
-        <v>96.01528016342493</v>
+        <v>94.5900664102256</v>
       </c>
       <c r="D34">
-        <v>135.031280163425</v>
+        <v>135.0990664102256</v>
       </c>
       <c r="E34">
-        <v>-40.32399999999999</v>
+        <v>-38.83099999999999</v>
       </c>
       <c r="F34">
-        <v>47.776</v>
+        <v>49.26900000000001</v>
       </c>
       <c r="G34">
         <v>8.76</v>
@@ -4057,28 +4057,28 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M34">
-        <v>2.9286688</v>
+        <v>3.0201897</v>
       </c>
       <c r="N34">
-        <v>7.642997866666667</v>
+        <v>7.551476966666667</v>
       </c>
       <c r="O34">
-        <v>1.528599573333334</v>
+        <v>1.510295393333333</v>
       </c>
       <c r="P34">
-        <v>6.114398293333333</v>
+        <v>6.041181573333334</v>
       </c>
       <c r="Q34">
-        <v>6.259398293333333</v>
+        <v>6.186181573333333</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08108069721057651</v>
+        <v>0.0815307635099843</v>
       </c>
       <c r="T34">
-        <v>0.7254082682266644</v>
+        <v>0.7346621050454762</v>
       </c>
       <c r="U34">
         <v>0.0613</v>
@@ -4095,7 +4095,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.609717379673204</v>
+        <v>3.500332004531591</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4103,22 +4103,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07080881155168947</v>
+        <v>0.07155154900018693</v>
       </c>
       <c r="C35">
-        <v>94.5900664102256</v>
+        <v>90.47831994214869</v>
       </c>
       <c r="D35">
-        <v>135.0990664102256</v>
+        <v>132.4803199421487</v>
       </c>
       <c r="E35">
-        <v>-38.83099999999999</v>
+        <v>-37.33799999999999</v>
       </c>
       <c r="F35">
-        <v>49.26900000000001</v>
+        <v>50.76200000000001</v>
       </c>
       <c r="G35">
         <v>8.76</v>
@@ -4139,45 +4139,45 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M35">
-        <v>3.0201897</v>
+        <v>3.253844200000001</v>
       </c>
       <c r="N35">
-        <v>7.551476966666667</v>
+        <v>7.317822466666667</v>
       </c>
       <c r="O35">
-        <v>1.510295393333333</v>
+        <v>1.463564493333333</v>
       </c>
       <c r="P35">
-        <v>6.041181573333334</v>
+        <v>5.854257973333334</v>
       </c>
       <c r="Q35">
-        <v>6.186181573333333</v>
+        <v>5.999257973333333</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.0815307635099843</v>
+        <v>0.0819944681821014</v>
       </c>
       <c r="T35">
-        <v>0.7346621050454762</v>
+        <v>0.7441963611618279</v>
       </c>
       <c r="U35">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V35">
         <v>0.2</v>
       </c>
       <c r="W35">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y35">
-        <v>3.500332004531591</v>
+        <v>3.24897752223867</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4185,22 +4185,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07155154900018693</v>
+        <v>0.07155508644868439</v>
       </c>
       <c r="C36">
-        <v>90.47831994214869</v>
+        <v>88.97309048479509</v>
       </c>
       <c r="D36">
-        <v>132.4803199421487</v>
+        <v>132.4680904847951</v>
       </c>
       <c r="E36">
-        <v>-37.33799999999999</v>
+        <v>-35.84499999999998</v>
       </c>
       <c r="F36">
-        <v>50.76200000000001</v>
+        <v>52.25500000000001</v>
       </c>
       <c r="G36">
         <v>8.76</v>
@@ -4221,28 +4221,28 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M36">
-        <v>3.253844200000001</v>
+        <v>3.349545500000001</v>
       </c>
       <c r="N36">
-        <v>7.317822466666667</v>
+        <v>7.222121166666666</v>
       </c>
       <c r="O36">
-        <v>1.463564493333333</v>
+        <v>1.444424233333333</v>
       </c>
       <c r="P36">
-        <v>5.854257973333334</v>
+        <v>5.777696933333333</v>
       </c>
       <c r="Q36">
-        <v>5.999257973333333</v>
+        <v>5.922696933333333</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.0819944681821014</v>
+        <v>0.08247244069028367</v>
       </c>
       <c r="T36">
-        <v>0.7441963611618279</v>
+        <v>0.7540239790048365</v>
       </c>
       <c r="U36">
         <v>0.0641</v>
@@ -4259,7 +4259,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.24897752223867</v>
+        <v>3.15614959303185</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4267,22 +4267,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07155508644868439</v>
+        <v>0.07155862389718183</v>
       </c>
       <c r="C37">
-        <v>88.97309048479509</v>
+        <v>87.4678632850723</v>
       </c>
       <c r="D37">
-        <v>132.4680904847951</v>
+        <v>132.4558632850723</v>
       </c>
       <c r="E37">
-        <v>-35.84499999999998</v>
+        <v>-34.35199999999998</v>
       </c>
       <c r="F37">
-        <v>52.25500000000001</v>
+        <v>53.74800000000001</v>
       </c>
       <c r="G37">
         <v>8.76</v>
@@ -4303,28 +4303,28 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M37">
-        <v>3.349545500000001</v>
+        <v>3.445246800000001</v>
       </c>
       <c r="N37">
-        <v>7.222121166666666</v>
+        <v>7.126419866666666</v>
       </c>
       <c r="O37">
-        <v>1.444424233333333</v>
+        <v>1.425283973333333</v>
       </c>
       <c r="P37">
-        <v>5.777696933333333</v>
+        <v>5.701135893333332</v>
       </c>
       <c r="Q37">
-        <v>5.922696933333333</v>
+        <v>5.846135893333332</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08247244069028367</v>
+        <v>0.08296534983934663</v>
       </c>
       <c r="T37">
-        <v>0.7540239790048365</v>
+        <v>0.7641587099054392</v>
       </c>
       <c r="U37">
         <v>0.0641</v>
@@ -4341,7 +4341,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.15614959303185</v>
+        <v>3.068478771003187</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4349,22 +4349,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07155862389718183</v>
+        <v>0.0738709613456793</v>
       </c>
       <c r="C38">
-        <v>87.46786328507231</v>
+        <v>78.43775975286172</v>
       </c>
       <c r="D38">
-        <v>132.4558632850723</v>
+        <v>124.9187597528617</v>
       </c>
       <c r="E38">
-        <v>-34.35199999999999</v>
+        <v>-32.85899999999999</v>
       </c>
       <c r="F38">
-        <v>53.748</v>
+        <v>55.24100000000001</v>
       </c>
       <c r="G38">
         <v>8.76</v>
@@ -4385,45 +4385,45 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M38">
-        <v>3.4452468</v>
+        <v>3.971827900000001</v>
       </c>
       <c r="N38">
-        <v>7.126419866666667</v>
+        <v>6.599838766666666</v>
       </c>
       <c r="O38">
-        <v>1.425283973333333</v>
+        <v>1.319967753333333</v>
       </c>
       <c r="P38">
-        <v>5.701135893333333</v>
+        <v>5.279871013333333</v>
       </c>
       <c r="Q38">
-        <v>5.846135893333333</v>
+        <v>5.424871013333332</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08296534983934661</v>
+        <v>0.08347390689790364</v>
       </c>
       <c r="T38">
-        <v>0.7641587099054391</v>
+        <v>0.7746151782949499</v>
       </c>
       <c r="U38">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V38">
         <v>0.2</v>
       </c>
       <c r="W38">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y38">
-        <v>3.068478771003188</v>
+        <v>2.661662824481057</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4431,22 +4431,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.0738709613456793</v>
+        <v>0.07393689879417675</v>
       </c>
       <c r="C39">
-        <v>78.43775975286172</v>
+        <v>76.74239365258757</v>
       </c>
       <c r="D39">
-        <v>124.9187597528617</v>
+        <v>124.7163936525876</v>
       </c>
       <c r="E39">
-        <v>-32.85899999999999</v>
+        <v>-31.36599999999999</v>
       </c>
       <c r="F39">
-        <v>55.24100000000001</v>
+        <v>56.734</v>
       </c>
       <c r="G39">
         <v>8.76</v>
@@ -4467,28 +4467,28 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M39">
-        <v>3.971827900000001</v>
+        <v>4.079174600000001</v>
       </c>
       <c r="N39">
-        <v>6.599838766666666</v>
+        <v>6.492492066666666</v>
       </c>
       <c r="O39">
-        <v>1.319967753333333</v>
+        <v>1.298498413333333</v>
       </c>
       <c r="P39">
-        <v>5.279871013333333</v>
+        <v>5.193993653333333</v>
       </c>
       <c r="Q39">
-        <v>5.424871013333332</v>
+        <v>5.338993653333333</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08347390689790364</v>
+        <v>0.08399886902286571</v>
       </c>
       <c r="T39">
-        <v>0.7746151782949499</v>
+        <v>0.7854089521163802</v>
       </c>
       <c r="U39">
         <v>0.07190000000000001</v>
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.661662824481057</v>
+        <v>2.591619065942082</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4513,22 +4513,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07393689879417675</v>
+        <v>0.0740028362426742</v>
       </c>
       <c r="C40">
-        <v>76.74239365258757</v>
+        <v>75.04768215061981</v>
       </c>
       <c r="D40">
-        <v>124.7163936525876</v>
+        <v>124.5146821506198</v>
       </c>
       <c r="E40">
-        <v>-31.36599999999999</v>
+        <v>-29.87299999999999</v>
       </c>
       <c r="F40">
-        <v>56.734</v>
+        <v>58.227</v>
       </c>
       <c r="G40">
         <v>8.76</v>
@@ -4549,28 +4549,28 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M40">
-        <v>4.079174600000001</v>
+        <v>4.186521300000001</v>
       </c>
       <c r="N40">
-        <v>6.492492066666666</v>
+        <v>6.385145366666666</v>
       </c>
       <c r="O40">
-        <v>1.298498413333333</v>
+        <v>1.277029073333333</v>
       </c>
       <c r="P40">
-        <v>5.193993653333333</v>
+        <v>5.108116293333334</v>
       </c>
       <c r="Q40">
-        <v>5.338993653333333</v>
+        <v>5.253116293333333</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08399886902286571</v>
+        <v>0.08454104302077736</v>
       </c>
       <c r="T40">
-        <v>0.7854089521163802</v>
+        <v>0.796556620161464</v>
       </c>
       <c r="U40">
         <v>0.07190000000000001</v>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.591619065942082</v>
+        <v>2.52516729502049</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4595,22 +4595,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.0740028362426742</v>
+        <v>0.07531677369117165</v>
       </c>
       <c r="C41">
-        <v>75.04768215061981</v>
+        <v>69.66697009512049</v>
       </c>
       <c r="D41">
-        <v>124.5146821506198</v>
+        <v>120.6269700951205</v>
       </c>
       <c r="E41">
-        <v>-29.87299999999999</v>
+        <v>-28.37999999999999</v>
       </c>
       <c r="F41">
-        <v>58.227</v>
+        <v>59.72000000000001</v>
       </c>
       <c r="G41">
         <v>8.76</v>
@@ -4631,45 +4631,45 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M41">
-        <v>4.186521300000001</v>
+        <v>4.526776000000001</v>
       </c>
       <c r="N41">
-        <v>6.385145366666666</v>
+        <v>6.044890666666666</v>
       </c>
       <c r="O41">
-        <v>1.277029073333333</v>
+        <v>1.208978133333333</v>
       </c>
       <c r="P41">
-        <v>5.108116293333334</v>
+        <v>4.835912533333333</v>
       </c>
       <c r="Q41">
-        <v>5.253116293333333</v>
+        <v>4.980912533333333</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08454104302077736</v>
+        <v>0.08510128948528609</v>
       </c>
       <c r="T41">
-        <v>0.796556620161464</v>
+        <v>0.808075877141384</v>
       </c>
       <c r="U41">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V41">
         <v>0.2</v>
       </c>
       <c r="W41">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y41">
-        <v>2.52516729502049</v>
+        <v>2.335363328485144</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4677,22 +4677,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07531677369117165</v>
+        <v>0.07541391113966911</v>
       </c>
       <c r="C42">
-        <v>69.66697009512049</v>
+        <v>67.89617240119658</v>
       </c>
       <c r="D42">
-        <v>120.6269700951205</v>
+        <v>120.3491724011966</v>
       </c>
       <c r="E42">
-        <v>-28.37999999999999</v>
+        <v>-26.88699999999999</v>
       </c>
       <c r="F42">
-        <v>59.72000000000001</v>
+        <v>61.21300000000001</v>
       </c>
       <c r="G42">
         <v>8.76</v>
@@ -4713,28 +4713,28 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M42">
-        <v>4.526776000000001</v>
+        <v>4.639945400000001</v>
       </c>
       <c r="N42">
-        <v>6.044890666666666</v>
+        <v>5.931721266666666</v>
       </c>
       <c r="O42">
-        <v>1.208978133333333</v>
+        <v>1.186344253333333</v>
       </c>
       <c r="P42">
-        <v>4.835912533333333</v>
+        <v>4.745377013333333</v>
       </c>
       <c r="Q42">
-        <v>4.980912533333333</v>
+        <v>4.890377013333333</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08510128948528609</v>
+        <v>0.08568052735537136</v>
       </c>
       <c r="T42">
-        <v>0.808075877141384</v>
+        <v>0.8199856174087589</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.335363328485144</v>
+        <v>2.278403247302579</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07541391113966911</v>
+        <v>0.07551104858816657</v>
       </c>
       <c r="C43">
-        <v>67.89617240119658</v>
+        <v>66.12665127494097</v>
       </c>
       <c r="D43">
-        <v>120.3491724011966</v>
+        <v>120.072651274941</v>
       </c>
       <c r="E43">
-        <v>-26.88699999999999</v>
+        <v>-25.39399999999998</v>
       </c>
       <c r="F43">
-        <v>61.21300000000001</v>
+        <v>62.70600000000001</v>
       </c>
       <c r="G43">
         <v>8.76</v>
@@ -4795,28 +4795,28 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M43">
-        <v>4.639945400000001</v>
+        <v>4.753114800000001</v>
       </c>
       <c r="N43">
-        <v>5.931721266666666</v>
+        <v>5.818551866666666</v>
       </c>
       <c r="O43">
-        <v>1.186344253333333</v>
+        <v>1.163710373333333</v>
       </c>
       <c r="P43">
-        <v>4.745377013333333</v>
+        <v>4.654841493333333</v>
       </c>
       <c r="Q43">
-        <v>4.890377013333333</v>
+        <v>4.799841493333332</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08568052735537136</v>
+        <v>0.08627973894511476</v>
       </c>
       <c r="T43">
-        <v>0.8199856174087589</v>
+        <v>0.8323060383750088</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4833,7 +4833,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.278403247302579</v>
+        <v>2.224155550938232</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4841,22 +4841,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07551104858816657</v>
+        <v>0.07560818603666403</v>
       </c>
       <c r="C44">
-        <v>66.12665127494098</v>
+        <v>64.35839793718098</v>
       </c>
       <c r="D44">
-        <v>120.072651274941</v>
+        <v>119.797397937181</v>
       </c>
       <c r="E44">
-        <v>-25.39399999999999</v>
+        <v>-23.901</v>
       </c>
       <c r="F44">
-        <v>62.706</v>
+        <v>64.199</v>
       </c>
       <c r="G44">
         <v>8.76</v>
@@ -4877,28 +4877,28 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M44">
-        <v>4.753114800000001</v>
+        <v>4.8662842</v>
       </c>
       <c r="N44">
-        <v>5.818551866666667</v>
+        <v>5.705382466666667</v>
       </c>
       <c r="O44">
-        <v>1.163710373333333</v>
+        <v>1.141076493333333</v>
       </c>
       <c r="P44">
-        <v>4.654841493333334</v>
+        <v>4.564305973333334</v>
       </c>
       <c r="Q44">
-        <v>4.799841493333333</v>
+        <v>4.709305973333334</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08627973894511476</v>
+        <v>0.08689997550291932</v>
       </c>
       <c r="T44">
-        <v>0.8323060383750086</v>
+        <v>0.8450587548137586</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.224155550938232</v>
+        <v>2.172431003241995</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4923,22 +4923,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07560818603666403</v>
+        <v>0.07570532348516147</v>
       </c>
       <c r="C45">
-        <v>64.35839793718098</v>
+        <v>62.59140368906102</v>
       </c>
       <c r="D45">
-        <v>119.797397937181</v>
+        <v>119.523403689061</v>
       </c>
       <c r="E45">
-        <v>-23.901</v>
+        <v>-22.40799999999999</v>
       </c>
       <c r="F45">
-        <v>64.199</v>
+        <v>65.69200000000001</v>
       </c>
       <c r="G45">
         <v>8.76</v>
@@ -4959,28 +4959,28 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M45">
-        <v>4.8662842</v>
+        <v>4.979453600000001</v>
       </c>
       <c r="N45">
-        <v>5.705382466666667</v>
+        <v>5.592213066666666</v>
       </c>
       <c r="O45">
-        <v>1.141076493333333</v>
+        <v>1.118442613333333</v>
       </c>
       <c r="P45">
-        <v>4.564305973333334</v>
+        <v>4.473770453333333</v>
       </c>
       <c r="Q45">
-        <v>4.709305973333334</v>
+        <v>4.618770453333332</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08689997550291932</v>
+        <v>0.08754236336635976</v>
       </c>
       <c r="T45">
-        <v>0.8450587548137586</v>
+        <v>0.8582669254110351</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.172431003241995</v>
+        <v>2.123057571350131</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5005,22 +5005,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07570532348516147</v>
+        <v>0.07580246093365892</v>
       </c>
       <c r="C46">
-        <v>62.59140368906102</v>
+        <v>60.82565991112614</v>
       </c>
       <c r="D46">
-        <v>119.523403689061</v>
+        <v>119.2506599111261</v>
       </c>
       <c r="E46">
-        <v>-22.40799999999999</v>
+        <v>-20.91499999999999</v>
       </c>
       <c r="F46">
-        <v>65.69200000000001</v>
+        <v>67.185</v>
       </c>
       <c r="G46">
         <v>8.76</v>
@@ -5041,28 +5041,28 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M46">
-        <v>4.979453600000001</v>
+        <v>5.092623000000001</v>
       </c>
       <c r="N46">
-        <v>5.592213066666666</v>
+        <v>5.479043666666667</v>
       </c>
       <c r="O46">
-        <v>1.118442613333333</v>
+        <v>1.095808733333333</v>
       </c>
       <c r="P46">
-        <v>4.473770453333333</v>
+        <v>4.383234933333333</v>
       </c>
       <c r="Q46">
-        <v>4.618770453333332</v>
+        <v>4.528234933333333</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08754236336635976</v>
+        <v>0.08820811078847075</v>
       </c>
       <c r="T46">
-        <v>0.8582669254110351</v>
+        <v>0.8719553931209399</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5079,7 +5079,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.123057571350131</v>
+        <v>2.075878514209017</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5087,22 +5087,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07580246093365892</v>
+        <v>0.07589959838215637</v>
       </c>
       <c r="C47">
-        <v>60.82565991112614</v>
+        <v>59.06115806241809</v>
       </c>
       <c r="D47">
-        <v>119.2506599111261</v>
+        <v>118.9791580624181</v>
       </c>
       <c r="E47">
-        <v>-20.91499999999999</v>
+        <v>-19.42199999999998</v>
       </c>
       <c r="F47">
-        <v>67.185</v>
+        <v>68.67800000000001</v>
       </c>
       <c r="G47">
         <v>8.76</v>
@@ -5123,28 +5123,28 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M47">
-        <v>5.092623000000001</v>
+        <v>5.205792400000001</v>
       </c>
       <c r="N47">
-        <v>5.479043666666667</v>
+        <v>5.365874266666666</v>
       </c>
       <c r="O47">
-        <v>1.095808733333333</v>
+        <v>1.073174853333333</v>
       </c>
       <c r="P47">
-        <v>4.383234933333333</v>
+        <v>4.292699413333333</v>
       </c>
       <c r="Q47">
-        <v>4.528234933333333</v>
+        <v>4.437699413333332</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08820811078847075</v>
+        <v>0.0888985155225118</v>
       </c>
       <c r="T47">
-        <v>0.8719553931209399</v>
+        <v>0.886150841116397</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5161,7 +5161,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.075878514209017</v>
+        <v>2.030750720421864</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5169,22 +5169,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07589959838215637</v>
+        <v>0.08133593583065382</v>
       </c>
       <c r="C48">
-        <v>59.06115806241809</v>
+        <v>44.12140167375158</v>
       </c>
       <c r="D48">
-        <v>118.9791580624181</v>
+        <v>105.5324016737516</v>
       </c>
       <c r="E48">
-        <v>-19.42199999999998</v>
+        <v>-17.92899999999999</v>
       </c>
       <c r="F48">
-        <v>68.67800000000001</v>
+        <v>70.17100000000001</v>
       </c>
       <c r="G48">
         <v>8.76</v>
@@ -5205,45 +5205,45 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M48">
-        <v>5.205792400000001</v>
+        <v>6.315390000000001</v>
       </c>
       <c r="N48">
-        <v>5.365874266666666</v>
+        <v>4.256276666666666</v>
       </c>
       <c r="O48">
-        <v>1.073174853333333</v>
+        <v>0.8512553333333334</v>
       </c>
       <c r="P48">
-        <v>4.292699413333333</v>
+        <v>3.405021333333333</v>
       </c>
       <c r="Q48">
-        <v>4.437699413333332</v>
+        <v>3.550021333333333</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.0888985155225118</v>
+        <v>0.08961497326538456</v>
       </c>
       <c r="T48">
-        <v>0.886150841116397</v>
+        <v>0.9008819663947013</v>
       </c>
       <c r="U48">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V48">
         <v>0.2</v>
       </c>
       <c r="W48">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y48">
-        <v>2.030750720421864</v>
+        <v>1.673953099755782</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5251,22 +5251,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08133593583065382</v>
+        <v>0.08154667327915127</v>
       </c>
       <c r="C49">
-        <v>44.12140167375158</v>
+        <v>42.16807170280825</v>
       </c>
       <c r="D49">
-        <v>105.5324016737516</v>
+        <v>105.0720717028083</v>
       </c>
       <c r="E49">
-        <v>-17.92899999999999</v>
+        <v>-16.43599999999998</v>
       </c>
       <c r="F49">
-        <v>70.17100000000001</v>
+        <v>71.66400000000002</v>
       </c>
       <c r="G49">
         <v>8.76</v>
@@ -5287,28 +5287,28 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M49">
-        <v>6.315390000000001</v>
+        <v>6.449760000000001</v>
       </c>
       <c r="N49">
-        <v>4.256276666666666</v>
+        <v>4.121906666666666</v>
       </c>
       <c r="O49">
-        <v>0.8512553333333334</v>
+        <v>0.8243813333333332</v>
       </c>
       <c r="P49">
-        <v>3.405021333333333</v>
+        <v>3.297525333333333</v>
       </c>
       <c r="Q49">
-        <v>3.550021333333333</v>
+        <v>3.442525333333333</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.08961497326538456</v>
+        <v>0.09035898707529091</v>
       </c>
       <c r="T49">
-        <v>0.9008819663947013</v>
+        <v>0.9161796734144788</v>
       </c>
       <c r="U49">
         <v>0.09</v>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.673953099755782</v>
+        <v>1.639079076844203</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5333,22 +5333,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08154667327915127</v>
+        <v>0.08175741072764872</v>
       </c>
       <c r="C50">
-        <v>42.16807170280826</v>
+        <v>40.21874018871873</v>
       </c>
       <c r="D50">
-        <v>105.0720717028083</v>
+        <v>104.6157401887187</v>
       </c>
       <c r="E50">
-        <v>-16.43599999999999</v>
+        <v>-14.94299999999998</v>
       </c>
       <c r="F50">
-        <v>71.664</v>
+        <v>73.15700000000001</v>
       </c>
       <c r="G50">
         <v>8.76</v>
@@ -5369,28 +5369,28 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M50">
-        <v>6.449759999999999</v>
+        <v>6.584130000000001</v>
       </c>
       <c r="N50">
-        <v>4.121906666666668</v>
+        <v>3.987536666666666</v>
       </c>
       <c r="O50">
-        <v>0.8243813333333336</v>
+        <v>0.7975073333333333</v>
       </c>
       <c r="P50">
-        <v>3.297525333333334</v>
+        <v>3.190029333333333</v>
       </c>
       <c r="Q50">
-        <v>3.442525333333334</v>
+        <v>3.335029333333333</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09035898707529091</v>
+        <v>0.09113217789735045</v>
       </c>
       <c r="T50">
-        <v>0.9161796734144788</v>
+        <v>0.9320772905134633</v>
       </c>
       <c r="U50">
         <v>0.09</v>
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.639079076844203</v>
+        <v>1.605628483439219</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5415,22 +5415,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08175741072764872</v>
+        <v>0.08196814817614617</v>
       </c>
       <c r="C51">
-        <v>40.21874018871873</v>
+        <v>38.27335526046586</v>
       </c>
       <c r="D51">
-        <v>104.6157401887187</v>
+        <v>104.1633552604659</v>
       </c>
       <c r="E51">
-        <v>-14.94299999999998</v>
+        <v>-13.44999999999999</v>
       </c>
       <c r="F51">
-        <v>73.15700000000001</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="G51">
         <v>8.76</v>
@@ -5451,28 +5451,28 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M51">
-        <v>6.584130000000001</v>
+        <v>6.718500000000001</v>
       </c>
       <c r="N51">
-        <v>3.987536666666666</v>
+        <v>3.853166666666667</v>
       </c>
       <c r="O51">
-        <v>0.7975073333333333</v>
+        <v>0.7706333333333334</v>
       </c>
       <c r="P51">
-        <v>3.190029333333333</v>
+        <v>3.082533333333333</v>
       </c>
       <c r="Q51">
-        <v>3.335029333333333</v>
+        <v>3.227533333333333</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09113217789735045</v>
+        <v>0.09193629635229236</v>
       </c>
       <c r="T51">
-        <v>0.9320772905134633</v>
+        <v>0.9486108122964073</v>
       </c>
       <c r="U51">
         <v>0.09</v>
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.605628483439219</v>
+        <v>1.573515913770435</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5497,22 +5497,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08196814817614617</v>
+        <v>0.08217888562464362</v>
       </c>
       <c r="C52">
-        <v>38.27335526046586</v>
+        <v>36.33186594038307</v>
       </c>
       <c r="D52">
-        <v>104.1633552604659</v>
+        <v>103.7148659403831</v>
       </c>
       <c r="E52">
-        <v>-13.44999999999999</v>
+        <v>-11.95699999999999</v>
       </c>
       <c r="F52">
-        <v>74.65000000000001</v>
+        <v>76.143</v>
       </c>
       <c r="G52">
         <v>8.76</v>
@@ -5533,28 +5533,28 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M52">
-        <v>6.718500000000001</v>
+        <v>6.85287</v>
       </c>
       <c r="N52">
-        <v>3.853166666666667</v>
+        <v>3.718796666666667</v>
       </c>
       <c r="O52">
-        <v>0.7706333333333334</v>
+        <v>0.7437593333333334</v>
       </c>
       <c r="P52">
-        <v>3.082533333333333</v>
+        <v>2.975037333333334</v>
       </c>
       <c r="Q52">
-        <v>3.227533333333333</v>
+        <v>3.120037333333334</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09193629635229236</v>
+        <v>0.09277323596866048</v>
       </c>
       <c r="T52">
-        <v>0.9486108122964073</v>
+        <v>0.9658191717031449</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.573515913770435</v>
+        <v>1.54266266055925</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5579,22 +5579,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08217888562464362</v>
+        <v>0.08238962307314107</v>
       </c>
       <c r="C53">
-        <v>36.33186594038307</v>
+        <v>34.39422212500455</v>
       </c>
       <c r="D53">
-        <v>103.7148659403831</v>
+        <v>103.2702221250046</v>
       </c>
       <c r="E53">
-        <v>-11.95699999999999</v>
+        <v>-10.46399999999998</v>
       </c>
       <c r="F53">
-        <v>76.143</v>
+        <v>77.63600000000001</v>
       </c>
       <c r="G53">
         <v>8.76</v>
@@ -5615,28 +5615,28 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M53">
-        <v>6.85287</v>
+        <v>6.987240000000001</v>
       </c>
       <c r="N53">
-        <v>3.718796666666667</v>
+        <v>3.584426666666666</v>
       </c>
       <c r="O53">
-        <v>0.7437593333333334</v>
+        <v>0.7168853333333334</v>
       </c>
       <c r="P53">
-        <v>2.975037333333334</v>
+        <v>2.867541333333333</v>
       </c>
       <c r="Q53">
-        <v>3.120037333333334</v>
+        <v>3.012541333333333</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09277323596866048</v>
+        <v>0.09364504806904392</v>
       </c>
       <c r="T53">
-        <v>0.9658191717031449</v>
+        <v>0.983744546085163</v>
       </c>
       <c r="U53">
         <v>0.09</v>
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.54266266055925</v>
+        <v>1.51299607093311</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5661,22 +5661,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08238962307314107</v>
+        <v>0.108327010030311</v>
       </c>
       <c r="C54">
-        <v>34.39422212500455</v>
+        <v>-2.768818901396969</v>
       </c>
       <c r="D54">
-        <v>103.2702221250046</v>
+        <v>67.60018109860303</v>
       </c>
       <c r="E54">
-        <v>-10.46399999999998</v>
+        <v>-8.970999999999989</v>
       </c>
       <c r="F54">
-        <v>77.63600000000001</v>
+        <v>79.129</v>
       </c>
       <c r="G54">
         <v>8.76</v>
@@ -5697,45 +5697,45 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M54">
-        <v>6.987240000000001</v>
+        <v>11.6161372</v>
       </c>
       <c r="N54">
-        <v>3.584426666666666</v>
+        <v>-1.044470533333335</v>
       </c>
       <c r="O54">
-        <v>0.7168853333333334</v>
+        <v>-0.2088941066666671</v>
       </c>
       <c r="P54">
-        <v>2.867541333333333</v>
+        <v>-0.8355764266666682</v>
       </c>
       <c r="Q54">
-        <v>3.012541333333333</v>
+        <v>-0.6905764266666682</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09364504806904392</v>
+        <v>0.09507373032818062</v>
       </c>
       <c r="T54">
-        <v>0.983744546085163</v>
+        <v>1.013119757047146</v>
       </c>
       <c r="U54">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.2</v>
+        <v>0.1820169043228357</v>
       </c>
       <c r="W54">
-        <v>0.07199999999999999</v>
+        <v>0.1200799184454077</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y54">
-        <v>1.51299607093311</v>
+        <v>0.9100845216141786</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5743,22 +5743,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.108327010030311</v>
+        <v>0.109337010030311</v>
       </c>
       <c r="C55">
-        <v>-2.768818901396969</v>
+        <v>-5.158977377252796</v>
       </c>
       <c r="D55">
-        <v>67.60018109860303</v>
+        <v>66.70302262274721</v>
       </c>
       <c r="E55">
-        <v>-8.970999999999989</v>
+        <v>-7.47799999999998</v>
       </c>
       <c r="F55">
-        <v>79.129</v>
+        <v>80.62200000000001</v>
       </c>
       <c r="G55">
         <v>8.76</v>
@@ -5779,37 +5779,37 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M55">
-        <v>11.6161372</v>
+        <v>11.8353096</v>
       </c>
       <c r="N55">
-        <v>-1.044470533333335</v>
+        <v>-1.263642933333337</v>
       </c>
       <c r="O55">
-        <v>-0.2088941066666671</v>
+        <v>-0.2527285866666674</v>
       </c>
       <c r="P55">
-        <v>-0.8355764266666682</v>
+        <v>-1.010914346666669</v>
       </c>
       <c r="Q55">
-        <v>-0.6905764266666682</v>
+        <v>-0.8659143466666694</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09507373032818062</v>
+        <v>0.09614489837879324</v>
       </c>
       <c r="T55">
-        <v>1.013119757047146</v>
+        <v>1.035144099591649</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.1820169043228357</v>
+        <v>0.1786462209094499</v>
       </c>
       <c r="W55">
-        <v>0.1200799184454077</v>
+        <v>0.1205747347704928</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.9100845216141786</v>
+        <v>0.8932311045472493</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.109337010030311</v>
+        <v>0.110347010030311</v>
       </c>
       <c r="C56">
-        <v>-5.158977377252796</v>
+        <v>-7.525634405145809</v>
       </c>
       <c r="D56">
-        <v>66.70302262274721</v>
+        <v>65.8293655948542</v>
       </c>
       <c r="E56">
-        <v>-7.47799999999998</v>
+        <v>-5.984999999999985</v>
       </c>
       <c r="F56">
-        <v>80.62200000000001</v>
+        <v>82.11500000000001</v>
       </c>
       <c r="G56">
         <v>8.76</v>
@@ -5861,37 +5861,37 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M56">
-        <v>11.8353096</v>
+        <v>12.054482</v>
       </c>
       <c r="N56">
-        <v>-1.263642933333337</v>
+        <v>-1.482815333333335</v>
       </c>
       <c r="O56">
-        <v>-0.2527285866666674</v>
+        <v>-0.2965630666666669</v>
       </c>
       <c r="P56">
-        <v>-1.010914346666669</v>
+        <v>-1.186252266666668</v>
       </c>
       <c r="Q56">
-        <v>-0.8659143466666694</v>
+        <v>-1.041252266666668</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09614489837879324</v>
+        <v>0.097263673898322</v>
       </c>
       <c r="T56">
-        <v>1.035144099591649</v>
+        <v>1.058147301804796</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.1786462209094499</v>
+        <v>0.1753981078020054</v>
       </c>
       <c r="W56">
-        <v>0.1205747347704928</v>
+        <v>0.1210515577746656</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5899,7 +5899,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8932311045472493</v>
+        <v>0.8769905390100268</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5907,22 +5907,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.110347010030311</v>
+        <v>0.111357010030311</v>
       </c>
       <c r="C57">
-        <v>-7.525634405145809</v>
+        <v>-9.869701492061168</v>
       </c>
       <c r="D57">
-        <v>65.8293655948542</v>
+        <v>64.97829850793885</v>
       </c>
       <c r="E57">
-        <v>-5.984999999999985</v>
+        <v>-4.491999999999976</v>
       </c>
       <c r="F57">
-        <v>82.11500000000001</v>
+        <v>83.60800000000002</v>
       </c>
       <c r="G57">
         <v>8.76</v>
@@ -5943,37 +5943,37 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M57">
-        <v>12.054482</v>
+        <v>12.2736544</v>
       </c>
       <c r="N57">
-        <v>-1.482815333333335</v>
+        <v>-1.701987733333336</v>
       </c>
       <c r="O57">
-        <v>-0.2965630666666669</v>
+        <v>-0.3403975466666673</v>
       </c>
       <c r="P57">
-        <v>-1.186252266666668</v>
+        <v>-1.361590186666669</v>
       </c>
       <c r="Q57">
-        <v>-1.041252266666668</v>
+        <v>-1.216590186666669</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.097263673898322</v>
+        <v>0.09843330285055657</v>
       </c>
       <c r="T57">
-        <v>1.058147301804796</v>
+        <v>1.082196104118542</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.1753981078020054</v>
+        <v>0.1722659987341124</v>
       </c>
       <c r="W57">
-        <v>0.1210515577746656</v>
+        <v>0.1215113513858323</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8769905390100268</v>
+        <v>0.8613299936705618</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5989,22 +5989,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.111357010030311</v>
+        <v>0.112367010030311</v>
       </c>
       <c r="C58">
-        <v>-9.869701492061168</v>
+        <v>-12.19204360937749</v>
       </c>
       <c r="D58">
-        <v>64.97829850793885</v>
+        <v>64.14895639062252</v>
       </c>
       <c r="E58">
-        <v>-4.491999999999976</v>
+        <v>-2.998999999999981</v>
       </c>
       <c r="F58">
-        <v>83.60800000000002</v>
+        <v>85.10100000000001</v>
       </c>
       <c r="G58">
         <v>8.76</v>
@@ -6025,37 +6025,37 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M58">
-        <v>12.2736544</v>
+        <v>12.4928268</v>
       </c>
       <c r="N58">
-        <v>-1.701987733333336</v>
+        <v>-1.921160133333336</v>
       </c>
       <c r="O58">
-        <v>-0.3403975466666673</v>
+        <v>-0.3842320266666672</v>
       </c>
       <c r="P58">
-        <v>-1.361590186666669</v>
+        <v>-1.536928106666669</v>
       </c>
       <c r="Q58">
-        <v>-1.216590186666669</v>
+        <v>-1.391928106666669</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09843330285055657</v>
+        <v>0.09965733314940675</v>
       </c>
       <c r="T58">
-        <v>1.082196104118542</v>
+        <v>1.107363455377113</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.1722659987341124</v>
+        <v>0.1692437882300052</v>
       </c>
       <c r="W58">
-        <v>0.1215113513858323</v>
+        <v>0.1219550118878353</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8613299936705618</v>
+        <v>0.8462189411500257</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6071,22 +6071,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.112367010030311</v>
+        <v>0.113377010030311</v>
       </c>
       <c r="C59">
-        <v>-12.19204360937749</v>
+        <v>-14.49348212519652</v>
       </c>
       <c r="D59">
-        <v>64.14895639062252</v>
+        <v>63.3405178748035</v>
       </c>
       <c r="E59">
-        <v>-2.998999999999981</v>
+        <v>-1.505999999999972</v>
       </c>
       <c r="F59">
-        <v>85.10100000000001</v>
+        <v>86.59400000000002</v>
       </c>
       <c r="G59">
         <v>8.76</v>
@@ -6107,37 +6107,37 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M59">
-        <v>12.4928268</v>
+        <v>12.7119992</v>
       </c>
       <c r="N59">
-        <v>-1.921160133333336</v>
+        <v>-2.140332533333337</v>
       </c>
       <c r="O59">
-        <v>-0.3842320266666672</v>
+        <v>-0.4280665066666675</v>
       </c>
       <c r="P59">
-        <v>-1.536928106666669</v>
+        <v>-1.71226602666667</v>
       </c>
       <c r="Q59">
-        <v>-1.391928106666669</v>
+        <v>-1.56726602666667</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.09965733314940675</v>
+        <v>0.100939650605345</v>
       </c>
       <c r="T59">
-        <v>1.107363455377113</v>
+        <v>1.133729251933711</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.1692437882300052</v>
+        <v>0.166325791881212</v>
       </c>
       <c r="W59">
-        <v>0.1219550118878353</v>
+        <v>0.1223833737518381</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8462189411500257</v>
+        <v>0.8316289594060597</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6153,22 +6153,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.113377010030311</v>
+        <v>0.114387010030311</v>
       </c>
       <c r="C60">
-        <v>-14.49348212519649</v>
+        <v>-16.77479751770363</v>
       </c>
       <c r="D60">
-        <v>63.3405178748035</v>
+        <v>62.55220248229637</v>
       </c>
       <c r="E60">
-        <v>-1.506</v>
+        <v>-0.01299999999999102</v>
       </c>
       <c r="F60">
-        <v>86.59399999999999</v>
+        <v>88.087</v>
       </c>
       <c r="G60">
         <v>8.76</v>
@@ -6189,37 +6189,37 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M60">
-        <v>12.7119992</v>
+        <v>12.9311716</v>
       </c>
       <c r="N60">
-        <v>-2.140332533333334</v>
+        <v>-2.359504933333335</v>
       </c>
       <c r="O60">
-        <v>-0.4280665066666668</v>
+        <v>-0.4719009866666671</v>
       </c>
       <c r="P60">
-        <v>-1.712266026666667</v>
+        <v>-1.887603946666668</v>
       </c>
       <c r="Q60">
-        <v>-1.567266026666667</v>
+        <v>-1.742603946666668</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.100939650605345</v>
+        <v>0.1022845201323046</v>
       </c>
       <c r="T60">
-        <v>1.13372925193371</v>
+        <v>1.161381184907703</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.166325791881212</v>
+        <v>0.1635067106628864</v>
       </c>
       <c r="W60">
-        <v>0.1223833737518381</v>
+        <v>0.1227972148746883</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.83162895940606</v>
+        <v>0.8175335533144317</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6235,22 +6235,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.114387010030311</v>
+        <v>0.115397010030311</v>
       </c>
       <c r="C61">
-        <v>-16.77479751770363</v>
+        <v>-19.03673188840196</v>
       </c>
       <c r="D61">
-        <v>62.55220248229637</v>
+        <v>61.78326811159803</v>
       </c>
       <c r="E61">
-        <v>-0.01299999999999102</v>
+        <v>1.480000000000004</v>
       </c>
       <c r="F61">
-        <v>88.087</v>
+        <v>89.58</v>
       </c>
       <c r="G61">
         <v>8.76</v>
@@ -6271,37 +6271,37 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M61">
-        <v>12.9311716</v>
+        <v>13.150344</v>
       </c>
       <c r="N61">
-        <v>-2.359504933333335</v>
+        <v>-2.578677333333333</v>
       </c>
       <c r="O61">
-        <v>-0.4719009866666671</v>
+        <v>-0.5157354666666667</v>
       </c>
       <c r="P61">
-        <v>-1.887603946666668</v>
+        <v>-2.062941866666667</v>
       </c>
       <c r="Q61">
-        <v>-1.742603946666668</v>
+        <v>-1.917941866666667</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1022845201323046</v>
+        <v>0.1036966331356122</v>
       </c>
       <c r="T61">
-        <v>1.161381184907703</v>
+        <v>1.190415714530396</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.1635067106628864</v>
+        <v>0.160781598818505</v>
       </c>
       <c r="W61">
-        <v>0.1227972148746883</v>
+        <v>0.1231972612934435</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8175335533144317</v>
+        <v>0.8039079940925247</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6317,22 +6317,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.115397010030311</v>
+        <v>0.1500119583113844</v>
       </c>
       <c r="C62">
-        <v>-19.03673188840196</v>
+        <v>-38.84337880784197</v>
       </c>
       <c r="D62">
-        <v>61.78326811159803</v>
+        <v>43.46962119215804</v>
       </c>
       <c r="E62">
-        <v>1.480000000000004</v>
+        <v>2.973000000000013</v>
       </c>
       <c r="F62">
-        <v>89.58</v>
+        <v>91.07300000000001</v>
       </c>
       <c r="G62">
         <v>8.76</v>
@@ -6353,45 +6353,45 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M62">
-        <v>13.150344</v>
+        <v>18.2874584</v>
       </c>
       <c r="N62">
-        <v>-2.578677333333333</v>
+        <v>-7.715791733333335</v>
       </c>
       <c r="O62">
-        <v>-0.5157354666666667</v>
+        <v>-1.543158346666667</v>
       </c>
       <c r="P62">
-        <v>-2.062941866666667</v>
+        <v>-6.172633386666668</v>
       </c>
       <c r="Q62">
-        <v>-1.917941866666667</v>
+        <v>-6.027633386666668</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1036966331356122</v>
+        <v>0.1068861577828675</v>
       </c>
       <c r="T62">
-        <v>1.190415714530396</v>
+        <v>1.255995698310822</v>
       </c>
       <c r="U62">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.160781598818505</v>
+        <v>0.1156165765130781</v>
       </c>
       <c r="W62">
-        <v>0.1231972612934435</v>
+        <v>0.1775841914361739</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y62">
-        <v>0.8039079940925247</v>
+        <v>0.5780828825653905</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6399,22 +6399,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1500119583113844</v>
+        <v>0.1515619583113844</v>
       </c>
       <c r="C63">
-        <v>-38.84337880784197</v>
+        <v>-40.90579697397174</v>
       </c>
       <c r="D63">
-        <v>43.46962119215804</v>
+        <v>42.90020302602827</v>
       </c>
       <c r="E63">
-        <v>2.973000000000013</v>
+        <v>4.466000000000008</v>
       </c>
       <c r="F63">
-        <v>91.07300000000001</v>
+        <v>92.566</v>
       </c>
       <c r="G63">
         <v>8.76</v>
@@ -6435,37 +6435,37 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M63">
-        <v>18.2874584</v>
+        <v>18.5872528</v>
       </c>
       <c r="N63">
-        <v>-7.715791733333335</v>
+        <v>-8.015586133333334</v>
       </c>
       <c r="O63">
-        <v>-1.543158346666667</v>
+        <v>-1.603117226666667</v>
       </c>
       <c r="P63">
-        <v>-6.172633386666668</v>
+        <v>-6.412468906666668</v>
       </c>
       <c r="Q63">
-        <v>-6.027633386666668</v>
+        <v>-6.267468906666668</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1068861577828675</v>
+        <v>0.1084936882508377</v>
       </c>
       <c r="T63">
-        <v>1.255995698310822</v>
+        <v>1.289048216687422</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.1156165765130781</v>
+        <v>0.1137517930209317</v>
       </c>
       <c r="W63">
-        <v>0.1775841914361739</v>
+        <v>0.1779586399613969</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5780828825653905</v>
+        <v>0.5687589651046585</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6481,22 +6481,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1515619583113844</v>
+        <v>0.1531119583113844</v>
       </c>
       <c r="C64">
-        <v>-40.90579697397174</v>
+        <v>-42.95349015732972</v>
       </c>
       <c r="D64">
-        <v>42.90020302602827</v>
+        <v>42.3455098426703</v>
       </c>
       <c r="E64">
-        <v>4.466000000000008</v>
+        <v>5.959000000000017</v>
       </c>
       <c r="F64">
-        <v>92.566</v>
+        <v>94.05900000000001</v>
       </c>
       <c r="G64">
         <v>8.76</v>
@@ -6517,37 +6517,37 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M64">
-        <v>18.5872528</v>
+        <v>18.8870472</v>
       </c>
       <c r="N64">
-        <v>-8.015586133333334</v>
+        <v>-8.315380533333334</v>
       </c>
       <c r="O64">
-        <v>-1.603117226666667</v>
+        <v>-1.663076106666667</v>
       </c>
       <c r="P64">
-        <v>-6.412468906666668</v>
+        <v>-6.652304426666667</v>
       </c>
       <c r="Q64">
-        <v>-6.267468906666668</v>
+        <v>-6.507304426666668</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1084936882508377</v>
+        <v>0.1101881122576171</v>
       </c>
       <c r="T64">
-        <v>1.289048216687422</v>
+        <v>1.323887357678974</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.1137517930209317</v>
+        <v>0.1119462090047265</v>
       </c>
       <c r="W64">
-        <v>0.1779586399613969</v>
+        <v>0.1783212012318509</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5687589651046585</v>
+        <v>0.5597310450236321</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6563,22 +6563,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1531119583113844</v>
+        <v>0.1546619583113844</v>
       </c>
       <c r="C65">
-        <v>-42.95349015732972</v>
+        <v>-44.98702224242243</v>
       </c>
       <c r="D65">
-        <v>42.3455098426703</v>
+        <v>41.80497775757758</v>
       </c>
       <c r="E65">
-        <v>5.959000000000017</v>
+        <v>7.452000000000012</v>
       </c>
       <c r="F65">
-        <v>94.05900000000001</v>
+        <v>95.55200000000001</v>
       </c>
       <c r="G65">
         <v>8.76</v>
@@ -6599,37 +6599,37 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M65">
-        <v>18.8870472</v>
+        <v>19.1868416</v>
       </c>
       <c r="N65">
-        <v>-8.315380533333334</v>
+        <v>-8.615174933333334</v>
       </c>
       <c r="O65">
-        <v>-1.663076106666667</v>
+        <v>-1.723034986666667</v>
       </c>
       <c r="P65">
-        <v>-6.652304426666667</v>
+        <v>-6.892139946666667</v>
       </c>
       <c r="Q65">
-        <v>-6.507304426666668</v>
+        <v>-6.747139946666667</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1101881122576171</v>
+        <v>0.1119766709314398</v>
       </c>
       <c r="T65">
-        <v>1.323887357678974</v>
+        <v>1.36066200650339</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1119462090047265</v>
+        <v>0.1101970494890276</v>
       </c>
       <c r="W65">
-        <v>0.1783212012318509</v>
+        <v>0.1786724324626033</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5597310450236321</v>
+        <v>0.550985247445138</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6645,22 +6645,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1546619583113844</v>
+        <v>0.1562119583113844</v>
       </c>
       <c r="C66">
-        <v>-44.98702224242243</v>
+        <v>-47.00692868514383</v>
       </c>
       <c r="D66">
-        <v>41.80497775757758</v>
+        <v>41.27807131485618</v>
       </c>
       <c r="E66">
-        <v>7.452000000000012</v>
+        <v>8.945000000000022</v>
       </c>
       <c r="F66">
-        <v>95.55200000000001</v>
+        <v>97.04500000000002</v>
       </c>
       <c r="G66">
         <v>8.76</v>
@@ -6681,37 +6681,37 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M66">
-        <v>19.1868416</v>
+        <v>19.486636</v>
       </c>
       <c r="N66">
-        <v>-8.615174933333334</v>
+        <v>-8.914969333333337</v>
       </c>
       <c r="O66">
-        <v>-1.723034986666667</v>
+        <v>-1.782993866666668</v>
       </c>
       <c r="P66">
-        <v>-6.892139946666667</v>
+        <v>-7.131975466666669</v>
       </c>
       <c r="Q66">
-        <v>-6.747139946666667</v>
+        <v>-6.98697546666667</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1119766709314398</v>
+        <v>0.1138674329580524</v>
       </c>
       <c r="T66">
-        <v>1.36066200650339</v>
+        <v>1.399538063832058</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1101970494890276</v>
+        <v>0.1085017102661195</v>
       </c>
       <c r="W66">
-        <v>0.1786724324626033</v>
+        <v>0.1790128565785632</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.550985247445138</v>
+        <v>0.5425085513305973</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6727,22 +6727,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1562119583113844</v>
+        <v>0.1577619583113844</v>
       </c>
       <c r="C67">
-        <v>-47.00692868514383</v>
+        <v>-49.01371828203489</v>
       </c>
       <c r="D67">
-        <v>41.27807131485618</v>
+        <v>40.76428171796512</v>
       </c>
       <c r="E67">
-        <v>8.945000000000022</v>
+        <v>10.43800000000002</v>
       </c>
       <c r="F67">
-        <v>97.04500000000002</v>
+        <v>98.53800000000001</v>
       </c>
       <c r="G67">
         <v>8.76</v>
@@ -6763,37 +6763,37 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M67">
-        <v>19.486636</v>
+        <v>19.7864304</v>
       </c>
       <c r="N67">
-        <v>-8.914969333333337</v>
+        <v>-9.214763733333337</v>
       </c>
       <c r="O67">
-        <v>-1.782993866666668</v>
+        <v>-1.842952746666668</v>
       </c>
       <c r="P67">
-        <v>-7.131975466666669</v>
+        <v>-7.371810986666669</v>
       </c>
       <c r="Q67">
-        <v>-6.98697546666667</v>
+        <v>-7.22681098666667</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1138674329580524</v>
+        <v>0.115869416280348</v>
       </c>
       <c r="T67">
-        <v>1.399538063832058</v>
+        <v>1.440700948062413</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1085017102661195</v>
+        <v>0.106857744959057</v>
       </c>
       <c r="W67">
-        <v>0.1790128565785632</v>
+        <v>0.1793429648122213</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5425085513305973</v>
+        <v>0.5342887247952852</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6809,22 +6809,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1577619583113844</v>
+        <v>0.1593119583113844</v>
       </c>
       <c r="C68">
-        <v>-49.01371828203489</v>
+        <v>-51.00787480903558</v>
       </c>
       <c r="D68">
-        <v>40.76428171796512</v>
+        <v>40.26312519096444</v>
       </c>
       <c r="E68">
-        <v>10.43800000000002</v>
+        <v>11.93100000000003</v>
       </c>
       <c r="F68">
-        <v>98.53800000000001</v>
+        <v>100.031</v>
       </c>
       <c r="G68">
         <v>8.76</v>
@@ -6845,37 +6845,37 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M68">
-        <v>19.7864304</v>
+        <v>20.0862248</v>
       </c>
       <c r="N68">
-        <v>-9.214763733333337</v>
+        <v>-9.514558133333336</v>
       </c>
       <c r="O68">
-        <v>-1.842952746666668</v>
+        <v>-1.902911626666667</v>
       </c>
       <c r="P68">
-        <v>-7.371810986666669</v>
+        <v>-7.611646506666669</v>
       </c>
       <c r="Q68">
-        <v>-7.22681098666667</v>
+        <v>-7.466646506666669</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.115869416280348</v>
+        <v>0.1179927319252071</v>
       </c>
       <c r="T68">
-        <v>1.440700948062413</v>
+        <v>1.484358552549153</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.106857744959057</v>
+        <v>0.1052628532432502</v>
       </c>
       <c r="W68">
-        <v>0.1793429648122213</v>
+        <v>0.1796632190687553</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5342887247952852</v>
+        <v>0.5263142662162511</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1593119583113844</v>
+        <v>0.1608619583113844</v>
       </c>
       <c r="C69">
-        <v>-51.00787480903558</v>
+        <v>-52.98985854082375</v>
       </c>
       <c r="D69">
-        <v>40.26312519096444</v>
+        <v>39.77414145917626</v>
       </c>
       <c r="E69">
-        <v>11.93100000000003</v>
+        <v>13.42400000000002</v>
       </c>
       <c r="F69">
-        <v>100.031</v>
+        <v>101.524</v>
       </c>
       <c r="G69">
         <v>8.76</v>
@@ -6927,37 +6927,37 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M69">
-        <v>20.0862248</v>
+        <v>20.3860192</v>
       </c>
       <c r="N69">
-        <v>-9.514558133333336</v>
+        <v>-9.814352533333336</v>
       </c>
       <c r="O69">
-        <v>-1.902911626666667</v>
+        <v>-1.962870506666667</v>
       </c>
       <c r="P69">
-        <v>-7.611646506666669</v>
+        <v>-7.851482026666669</v>
       </c>
       <c r="Q69">
-        <v>-7.466646506666669</v>
+        <v>-7.706482026666669</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1179927319252071</v>
+        <v>0.1202487547978698</v>
       </c>
       <c r="T69">
-        <v>1.484358552549153</v>
+        <v>1.530744757316314</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1052628532432502</v>
+        <v>0.1037148701073201</v>
       </c>
       <c r="W69">
-        <v>0.1796632190687553</v>
+        <v>0.1799740540824501</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5263142662162511</v>
+        <v>0.5185743505366004</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6973,22 +6973,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1608619583113844</v>
+        <v>0.1624119583113844</v>
       </c>
       <c r="C70">
-        <v>-52.98985854082375</v>
+        <v>-54.96010766077101</v>
       </c>
       <c r="D70">
-        <v>39.77414145917626</v>
+        <v>39.296892339229</v>
       </c>
       <c r="E70">
-        <v>13.42400000000002</v>
+        <v>14.91700000000002</v>
       </c>
       <c r="F70">
-        <v>101.524</v>
+        <v>103.017</v>
       </c>
       <c r="G70">
         <v>8.76</v>
@@ -7009,37 +7009,37 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M70">
-        <v>20.3860192</v>
+        <v>20.6858136</v>
       </c>
       <c r="N70">
-        <v>-9.814352533333336</v>
+        <v>-10.11414693333334</v>
       </c>
       <c r="O70">
-        <v>-1.962870506666667</v>
+        <v>-2.022829386666667</v>
       </c>
       <c r="P70">
-        <v>-7.851482026666669</v>
+        <v>-8.091317546666669</v>
       </c>
       <c r="Q70">
-        <v>-7.706482026666669</v>
+        <v>-7.94631754666667</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1202487547978698</v>
+        <v>0.1226503275332849</v>
       </c>
       <c r="T70">
-        <v>1.530744757316314</v>
+        <v>1.58012362045555</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1037148701073201</v>
+        <v>0.1022117560477937</v>
       </c>
       <c r="W70">
-        <v>0.1799740540824501</v>
+        <v>0.180275879385603</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5185743505366004</v>
+        <v>0.5110587802389686</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7055,22 +7055,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1624119583113844</v>
+        <v>0.1639619583113844</v>
       </c>
       <c r="C71">
-        <v>-54.96010766077101</v>
+        <v>-56.91903957059395</v>
       </c>
       <c r="D71">
-        <v>39.296892339229</v>
+        <v>38.83096042940607</v>
       </c>
       <c r="E71">
-        <v>14.91700000000002</v>
+        <v>16.41000000000003</v>
       </c>
       <c r="F71">
-        <v>103.017</v>
+        <v>104.51</v>
       </c>
       <c r="G71">
         <v>8.76</v>
@@ -7091,37 +7091,37 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M71">
-        <v>20.6858136</v>
+        <v>20.98560800000001</v>
       </c>
       <c r="N71">
-        <v>-10.11414693333334</v>
+        <v>-10.41394133333334</v>
       </c>
       <c r="O71">
-        <v>-2.022829386666667</v>
+        <v>-2.082788266666668</v>
       </c>
       <c r="P71">
-        <v>-8.091317546666669</v>
+        <v>-8.331153066666671</v>
       </c>
       <c r="Q71">
-        <v>-7.94631754666667</v>
+        <v>-8.186153066666671</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1226503275332849</v>
+        <v>0.1252120051177278</v>
       </c>
       <c r="T71">
-        <v>1.58012362045555</v>
+        <v>1.632794407804068</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1022117560477937</v>
+        <v>0.1007515881042538</v>
       </c>
       <c r="W71">
-        <v>0.180275879385603</v>
+        <v>0.1805690811086658</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5110587802389686</v>
+        <v>0.5037579405212689</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7137,22 +7137,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1639619583113844</v>
+        <v>0.1906302729744821</v>
       </c>
       <c r="C72">
-        <v>-56.91903957059395</v>
+        <v>-64.99134597628424</v>
       </c>
       <c r="D72">
-        <v>38.83096042940607</v>
+        <v>32.25165402371579</v>
       </c>
       <c r="E72">
-        <v>16.41000000000003</v>
+        <v>17.90300000000002</v>
       </c>
       <c r="F72">
-        <v>104.51</v>
+        <v>106.003</v>
       </c>
       <c r="G72">
         <v>8.76</v>
@@ -7173,45 +7173,45 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M72">
-        <v>20.98560800000001</v>
+        <v>24.9955074</v>
       </c>
       <c r="N72">
-        <v>-10.41394133333334</v>
+        <v>-14.42384073333334</v>
       </c>
       <c r="O72">
-        <v>-2.082788266666668</v>
+        <v>-2.884768146666667</v>
       </c>
       <c r="P72">
-        <v>-8.331153066666671</v>
+        <v>-11.53907258666667</v>
       </c>
       <c r="Q72">
-        <v>-8.186153066666671</v>
+        <v>-11.39407258666667</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1252120051177278</v>
+        <v>0.1288755730979863</v>
       </c>
       <c r="T72">
-        <v>1.632794407804068</v>
+        <v>1.708121221450293</v>
       </c>
       <c r="U72">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.1007515881042538</v>
+        <v>0.08458853423128883</v>
       </c>
       <c r="W72">
-        <v>0.1805690811086658</v>
+        <v>0.2158540236282621</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y72">
-        <v>0.5037579405212689</v>
+        <v>0.4229426711564441</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7219,22 +7219,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1906302729744821</v>
+        <v>0.1925302729744821</v>
       </c>
       <c r="C73">
-        <v>-64.99134597628421</v>
+        <v>-66.86902705211617</v>
       </c>
       <c r="D73">
-        <v>32.2516540237158</v>
+        <v>31.86697294788384</v>
       </c>
       <c r="E73">
-        <v>17.90300000000001</v>
+        <v>19.39600000000002</v>
       </c>
       <c r="F73">
-        <v>106.003</v>
+        <v>107.496</v>
       </c>
       <c r="G73">
         <v>8.76</v>
@@ -7255,37 +7255,37 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M73">
-        <v>24.9955074</v>
+        <v>25.3475568</v>
       </c>
       <c r="N73">
-        <v>-14.42384073333333</v>
+        <v>-14.77589013333334</v>
       </c>
       <c r="O73">
-        <v>-2.884768146666667</v>
+        <v>-2.955178026666667</v>
       </c>
       <c r="P73">
-        <v>-11.53907258666667</v>
+        <v>-11.82071210666667</v>
       </c>
       <c r="Q73">
-        <v>-11.39407258666667</v>
+        <v>-11.67571210666667</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1288755730979862</v>
+        <v>0.1318425578514857</v>
       </c>
       <c r="T73">
-        <v>1.708121221450292</v>
+        <v>1.769125550787802</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.08458853423128884</v>
+        <v>0.08341369347807648</v>
       </c>
       <c r="W73">
-        <v>0.2158540236282621</v>
+        <v>0.2161310510778696</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.4229426711564441</v>
+        <v>0.4170684673903824</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7301,22 +7301,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1925302729744821</v>
+        <v>0.1944302729744821</v>
       </c>
       <c r="C74">
-        <v>-66.86902705211617</v>
+        <v>-68.73763973655848</v>
       </c>
       <c r="D74">
-        <v>31.86697294788384</v>
+        <v>31.49136026344152</v>
       </c>
       <c r="E74">
-        <v>19.39600000000002</v>
+        <v>20.88900000000001</v>
       </c>
       <c r="F74">
-        <v>107.496</v>
+        <v>108.989</v>
       </c>
       <c r="G74">
         <v>8.76</v>
@@ -7337,37 +7337,37 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M74">
-        <v>25.3475568</v>
+        <v>25.6996062</v>
       </c>
       <c r="N74">
-        <v>-14.77589013333334</v>
+        <v>-15.12793953333333</v>
       </c>
       <c r="O74">
-        <v>-2.955178026666667</v>
+        <v>-3.025587906666667</v>
       </c>
       <c r="P74">
-        <v>-11.82071210666667</v>
+        <v>-12.10235162666667</v>
       </c>
       <c r="Q74">
-        <v>-11.67571210666667</v>
+        <v>-11.95735162666667</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1318425578514857</v>
+        <v>0.1350293192533926</v>
       </c>
       <c r="T74">
-        <v>1.769125550787802</v>
+        <v>1.834648719335499</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.08341369347807648</v>
+        <v>0.08227104014276038</v>
       </c>
       <c r="W74">
-        <v>0.2161310510778696</v>
+        <v>0.2164004887343371</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.4170684673903824</v>
+        <v>0.4113552007138018</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7383,22 +7383,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1944302729744821</v>
+        <v>0.1963302729744821</v>
       </c>
       <c r="C75">
-        <v>-68.73763973655848</v>
+        <v>-70.59750095855156</v>
       </c>
       <c r="D75">
-        <v>31.49136026344152</v>
+        <v>31.12449904144844</v>
       </c>
       <c r="E75">
-        <v>20.88900000000001</v>
+        <v>22.38200000000002</v>
       </c>
       <c r="F75">
-        <v>108.989</v>
+        <v>110.482</v>
       </c>
       <c r="G75">
         <v>8.76</v>
@@ -7419,37 +7419,37 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M75">
-        <v>25.6996062</v>
+        <v>26.0516556</v>
       </c>
       <c r="N75">
-        <v>-15.12793953333333</v>
+        <v>-15.47998893333334</v>
       </c>
       <c r="O75">
-        <v>-3.025587906666667</v>
+        <v>-3.095997786666667</v>
       </c>
       <c r="P75">
-        <v>-12.10235162666667</v>
+        <v>-12.38399114666667</v>
       </c>
       <c r="Q75">
-        <v>-11.95735162666667</v>
+        <v>-12.23899114666667</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1350293192533926</v>
+        <v>0.1384612161477539</v>
       </c>
       <c r="T75">
-        <v>1.834648719335499</v>
+        <v>1.905212131617633</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.08227104014276038</v>
+        <v>0.08115926933002036</v>
       </c>
       <c r="W75">
-        <v>0.2164004887343371</v>
+        <v>0.2166626442919812</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.4113552007138018</v>
+        <v>0.4057963466501018</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7465,22 +7465,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1963302729744821</v>
+        <v>0.1982302729744821</v>
       </c>
       <c r="C76">
-        <v>-70.59750095855156</v>
+        <v>-72.44891304873958</v>
       </c>
       <c r="D76">
-        <v>31.12449904144844</v>
+        <v>30.76608695126043</v>
       </c>
       <c r="E76">
-        <v>22.38200000000002</v>
+        <v>23.87500000000001</v>
       </c>
       <c r="F76">
-        <v>110.482</v>
+        <v>111.975</v>
       </c>
       <c r="G76">
         <v>8.76</v>
@@ -7501,37 +7501,37 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M76">
-        <v>26.0516556</v>
+        <v>26.403705</v>
       </c>
       <c r="N76">
-        <v>-15.47998893333334</v>
+        <v>-15.83203833333333</v>
       </c>
       <c r="O76">
-        <v>-3.095997786666667</v>
+        <v>-3.166407666666667</v>
       </c>
       <c r="P76">
-        <v>-12.38399114666667</v>
+        <v>-12.66563066666667</v>
       </c>
       <c r="Q76">
-        <v>-12.23899114666667</v>
+        <v>-12.52063066666667</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1384612161477539</v>
+        <v>0.1421676647936641</v>
       </c>
       <c r="T76">
-        <v>1.905212131617633</v>
+        <v>1.981420616882339</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.08115926933002036</v>
+        <v>0.08007714573895343</v>
       </c>
       <c r="W76">
-        <v>0.2166626442919812</v>
+        <v>0.2169178090347548</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.4057963466501018</v>
+        <v>0.4003857286947672</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7547,22 +7547,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1982302729744821</v>
+        <v>0.2001302729744821</v>
       </c>
       <c r="C77">
-        <v>-72.44891304873958</v>
+        <v>-74.29216457043026</v>
       </c>
       <c r="D77">
-        <v>30.76608695126043</v>
+        <v>30.41583542956974</v>
       </c>
       <c r="E77">
-        <v>23.87500000000001</v>
+        <v>25.36800000000001</v>
       </c>
       <c r="F77">
-        <v>111.975</v>
+        <v>113.468</v>
       </c>
       <c r="G77">
         <v>8.76</v>
@@ -7583,37 +7583,37 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M77">
-        <v>26.403705</v>
+        <v>26.7557544</v>
       </c>
       <c r="N77">
-        <v>-15.83203833333333</v>
+        <v>-16.18408773333334</v>
       </c>
       <c r="O77">
-        <v>-3.166407666666667</v>
+        <v>-3.236817546666667</v>
       </c>
       <c r="P77">
-        <v>-12.66563066666667</v>
+        <v>-12.94727018666667</v>
       </c>
       <c r="Q77">
-        <v>-12.52063066666667</v>
+        <v>-12.80227018666667</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1421676647936641</v>
+        <v>0.1461829841600667</v>
       </c>
       <c r="T77">
-        <v>1.981420616882339</v>
+        <v>2.063979809252436</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.08007714573895343</v>
+        <v>0.07902349908449352</v>
       </c>
       <c r="W77">
-        <v>0.2169178090347548</v>
+        <v>0.2171662589158764</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.4003857286947672</v>
+        <v>0.3951174954224675</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7629,22 +7629,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2001302729744821</v>
+        <v>0.2020302729744821</v>
       </c>
       <c r="C78">
-        <v>-74.29216457043026</v>
+        <v>-76.12753109443375</v>
       </c>
       <c r="D78">
-        <v>30.41583542956974</v>
+        <v>30.07346890556627</v>
       </c>
       <c r="E78">
-        <v>25.36800000000001</v>
+        <v>26.86100000000002</v>
       </c>
       <c r="F78">
-        <v>113.468</v>
+        <v>114.961</v>
       </c>
       <c r="G78">
         <v>8.76</v>
@@ -7665,37 +7665,37 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M78">
-        <v>26.7557544</v>
+        <v>27.1078038</v>
       </c>
       <c r="N78">
-        <v>-16.18408773333334</v>
+        <v>-16.53613713333333</v>
       </c>
       <c r="O78">
-        <v>-3.236817546666667</v>
+        <v>-3.307227426666667</v>
       </c>
       <c r="P78">
-        <v>-12.94727018666667</v>
+        <v>-13.22890970666667</v>
       </c>
       <c r="Q78">
-        <v>-12.80227018666667</v>
+        <v>-13.08390970666667</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1461829841600667</v>
+        <v>0.1505474617322435</v>
       </c>
       <c r="T78">
-        <v>2.063979809252436</v>
+        <v>2.153718061828629</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.07902349908449352</v>
+        <v>0.07799721987560398</v>
       </c>
       <c r="W78">
-        <v>0.2171662589158764</v>
+        <v>0.2174082555533326</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3951174954224675</v>
+        <v>0.38998609937802</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7711,22 +7711,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2020302729744821</v>
+        <v>0.2039302729744821</v>
       </c>
       <c r="C79">
-        <v>-76.12753109443375</v>
+        <v>-77.95527592215373</v>
       </c>
       <c r="D79">
-        <v>30.07346890556627</v>
+        <v>29.73872407784629</v>
       </c>
       <c r="E79">
-        <v>26.86100000000002</v>
+        <v>28.35400000000001</v>
       </c>
       <c r="F79">
-        <v>114.961</v>
+        <v>116.454</v>
       </c>
       <c r="G79">
         <v>8.76</v>
@@ -7747,37 +7747,37 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M79">
-        <v>27.1078038</v>
+        <v>27.4598532</v>
       </c>
       <c r="N79">
-        <v>-16.53613713333333</v>
+        <v>-16.88818653333333</v>
       </c>
       <c r="O79">
-        <v>-3.307227426666667</v>
+        <v>-3.377637306666667</v>
       </c>
       <c r="P79">
-        <v>-13.22890970666667</v>
+        <v>-13.51054922666667</v>
       </c>
       <c r="Q79">
-        <v>-13.08390970666667</v>
+        <v>-13.36554922666667</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1505474617322435</v>
+        <v>0.1553087099928001</v>
       </c>
       <c r="T79">
-        <v>2.153718061828629</v>
+        <v>2.251614337366294</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.07799721987560398</v>
+        <v>0.07699725551822445</v>
       </c>
       <c r="W79">
-        <v>0.2174082555533326</v>
+        <v>0.2176440471488027</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.38998609937802</v>
+        <v>0.3849862775911224</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7793,22 +7793,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2039302729744821</v>
+        <v>0.2058302729744821</v>
       </c>
       <c r="C80">
-        <v>-77.95527592215373</v>
+        <v>-79.77565076091824</v>
       </c>
       <c r="D80">
-        <v>29.73872407784629</v>
+        <v>29.41134923908178</v>
       </c>
       <c r="E80">
-        <v>28.35400000000001</v>
+        <v>29.84700000000002</v>
       </c>
       <c r="F80">
-        <v>116.454</v>
+        <v>117.947</v>
       </c>
       <c r="G80">
         <v>8.76</v>
@@ -7829,37 +7829,37 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M80">
-        <v>27.4598532</v>
+        <v>27.8119026</v>
       </c>
       <c r="N80">
-        <v>-16.88818653333333</v>
+        <v>-17.24023593333334</v>
       </c>
       <c r="O80">
-        <v>-3.377637306666667</v>
+        <v>-3.448047186666668</v>
       </c>
       <c r="P80">
-        <v>-13.51054922666667</v>
+        <v>-13.79218874666667</v>
       </c>
       <c r="Q80">
-        <v>-13.36554922666667</v>
+        <v>-13.64718874666667</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1553087099928001</v>
+        <v>0.1605234104686477</v>
       </c>
       <c r="T80">
-        <v>2.251614337366294</v>
+        <v>2.35883406771707</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.07699725551822445</v>
+        <v>0.07602260671419629</v>
       </c>
       <c r="W80">
-        <v>0.2176440471488027</v>
+        <v>0.2178738693367925</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3849862775911224</v>
+        <v>0.3801130335709814</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7875,22 +7875,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2058302729744821</v>
+        <v>0.2077302729744821</v>
       </c>
       <c r="C81">
-        <v>-79.77565076091824</v>
+        <v>-81.58889635519023</v>
       </c>
       <c r="D81">
-        <v>29.41134923908178</v>
+        <v>29.09110364480977</v>
       </c>
       <c r="E81">
-        <v>29.84700000000002</v>
+        <v>31.34000000000002</v>
       </c>
       <c r="F81">
-        <v>117.947</v>
+        <v>119.44</v>
       </c>
       <c r="G81">
         <v>8.76</v>
@@ -7911,37 +7911,37 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M81">
-        <v>27.8119026</v>
+        <v>28.16395200000001</v>
       </c>
       <c r="N81">
-        <v>-17.24023593333334</v>
+        <v>-17.59228533333334</v>
       </c>
       <c r="O81">
-        <v>-3.448047186666668</v>
+        <v>-3.518457066666667</v>
       </c>
       <c r="P81">
-        <v>-13.79218874666667</v>
+        <v>-14.07382826666667</v>
       </c>
       <c r="Q81">
-        <v>-13.64718874666667</v>
+        <v>-13.92882826666667</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1605234104686477</v>
+        <v>0.16625958099208</v>
       </c>
       <c r="T81">
-        <v>2.35883406771707</v>
+        <v>2.476775771102924</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.07602260671419629</v>
+        <v>0.07507232413026883</v>
       </c>
       <c r="W81">
-        <v>0.2178738693367925</v>
+        <v>0.2180979459700826</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3801130335709814</v>
+        <v>0.3753616206513442</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7957,22 +7957,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2077302729744821</v>
+        <v>0.2096302729744821</v>
       </c>
       <c r="C82">
-        <v>-81.58889635519023</v>
+        <v>-83.39524307698498</v>
       </c>
       <c r="D82">
-        <v>29.09110364480977</v>
+        <v>28.77775692301504</v>
       </c>
       <c r="E82">
-        <v>31.34000000000002</v>
+        <v>32.83300000000003</v>
       </c>
       <c r="F82">
-        <v>119.44</v>
+        <v>120.933</v>
       </c>
       <c r="G82">
         <v>8.76</v>
@@ -7993,37 +7993,37 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M82">
-        <v>28.16395200000001</v>
+        <v>28.51600140000001</v>
       </c>
       <c r="N82">
-        <v>-17.59228533333334</v>
+        <v>-17.94433473333334</v>
       </c>
       <c r="O82">
-        <v>-3.518457066666667</v>
+        <v>-3.588866946666669</v>
       </c>
       <c r="P82">
-        <v>-14.07382826666667</v>
+        <v>-14.35546778666667</v>
       </c>
       <c r="Q82">
-        <v>-13.92882826666667</v>
+        <v>-14.21046778666667</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.16625958099208</v>
+        <v>0.1725995589390316</v>
       </c>
       <c r="T82">
-        <v>2.476775771102924</v>
+        <v>2.607132390634657</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.07507232413026883</v>
+        <v>0.07414550531384576</v>
       </c>
       <c r="W82">
-        <v>0.2180979459700826</v>
+        <v>0.2183164898469952</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3753616206513442</v>
+        <v>0.3707275265692287</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8039,22 +8039,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2096302729744821</v>
+        <v>0.2115302729744821</v>
       </c>
       <c r="C83">
-        <v>-83.39524307698498</v>
+        <v>-85.19491147853662</v>
       </c>
       <c r="D83">
-        <v>28.77775692301504</v>
+        <v>28.47108852146339</v>
       </c>
       <c r="E83">
-        <v>32.83300000000003</v>
+        <v>34.32600000000002</v>
       </c>
       <c r="F83">
-        <v>120.933</v>
+        <v>122.426</v>
       </c>
       <c r="G83">
         <v>8.76</v>
@@ -8075,37 +8075,37 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M83">
-        <v>28.51600140000001</v>
+        <v>28.86805080000001</v>
       </c>
       <c r="N83">
-        <v>-17.94433473333334</v>
+        <v>-18.29638413333334</v>
       </c>
       <c r="O83">
-        <v>-3.588866946666669</v>
+        <v>-3.659276826666668</v>
       </c>
       <c r="P83">
-        <v>-14.35546778666667</v>
+        <v>-14.63710730666667</v>
       </c>
       <c r="Q83">
-        <v>-14.21046778666667</v>
+        <v>-14.49210730666667</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1725995589390316</v>
+        <v>0.179643978880089</v>
       </c>
       <c r="T83">
-        <v>2.607132390634657</v>
+        <v>2.751973079003249</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.07414550531384576</v>
+        <v>0.07324129183440863</v>
       </c>
       <c r="W83">
-        <v>0.2183164898469952</v>
+        <v>0.2185297033854464</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3707275265692287</v>
+        <v>0.366206459172043</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8121,22 +8121,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2115302729744821</v>
+        <v>0.2134302729744821</v>
       </c>
       <c r="C84">
-        <v>-85.19491147853662</v>
+        <v>-86.9881128100011</v>
       </c>
       <c r="D84">
-        <v>28.47108852146339</v>
+        <v>28.17088718999893</v>
       </c>
       <c r="E84">
-        <v>34.32600000000002</v>
+        <v>35.81900000000003</v>
       </c>
       <c r="F84">
-        <v>122.426</v>
+        <v>123.919</v>
       </c>
       <c r="G84">
         <v>8.76</v>
@@ -8157,37 +8157,37 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M84">
-        <v>28.86805080000001</v>
+        <v>29.22010020000001</v>
       </c>
       <c r="N84">
-        <v>-18.29638413333334</v>
+        <v>-18.64843353333334</v>
       </c>
       <c r="O84">
-        <v>-3.659276826666668</v>
+        <v>-3.729686706666668</v>
       </c>
       <c r="P84">
-        <v>-14.63710730666667</v>
+        <v>-14.91874682666667</v>
       </c>
       <c r="Q84">
-        <v>-14.49210730666667</v>
+        <v>-14.77374682666667</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.179643978880089</v>
+        <v>0.1875171541083295</v>
       </c>
       <c r="T84">
-        <v>2.751973079003249</v>
+        <v>2.913853848356382</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.07324129183440863</v>
+        <v>0.0723588666315844</v>
       </c>
       <c r="W84">
-        <v>0.2185297033854464</v>
+        <v>0.2187377792482724</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.366206459172043</v>
+        <v>0.3617943331579221</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8203,22 +8203,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2134302729744821</v>
+        <v>0.2153302729744821</v>
       </c>
       <c r="C85">
-        <v>-86.9881128100011</v>
+        <v>-88.77504950474793</v>
       </c>
       <c r="D85">
-        <v>28.17088718999893</v>
+        <v>27.8769504952521</v>
       </c>
       <c r="E85">
-        <v>35.81900000000003</v>
+        <v>37.31200000000003</v>
       </c>
       <c r="F85">
-        <v>123.919</v>
+        <v>125.412</v>
       </c>
       <c r="G85">
         <v>8.76</v>
@@ -8239,37 +8239,37 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M85">
-        <v>29.22010020000001</v>
+        <v>29.57214960000001</v>
       </c>
       <c r="N85">
-        <v>-18.64843353333334</v>
+        <v>-19.00048293333334</v>
       </c>
       <c r="O85">
-        <v>-3.729686706666668</v>
+        <v>-3.800096586666668</v>
       </c>
       <c r="P85">
-        <v>-14.91874682666667</v>
+        <v>-15.20038634666667</v>
       </c>
       <c r="Q85">
-        <v>-14.77374682666667</v>
+        <v>-15.05538634666667</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1875171541083295</v>
+        <v>0.1963744762401001</v>
       </c>
       <c r="T85">
-        <v>2.913853848356382</v>
+        <v>3.095969713878656</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.0723588666315844</v>
+        <v>0.07149745155263698</v>
       </c>
       <c r="W85">
-        <v>0.2187377792482724</v>
+        <v>0.2189409009238882</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3617943331579221</v>
+        <v>0.3574872577631849</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8285,22 +8285,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2153302729744821</v>
+        <v>0.2172302729744821</v>
       </c>
       <c r="C86">
-        <v>-88.77504950474793</v>
+        <v>-90.55591563458498</v>
       </c>
       <c r="D86">
-        <v>27.87695049525208</v>
+        <v>27.58908436541502</v>
       </c>
       <c r="E86">
-        <v>37.31200000000001</v>
+        <v>38.80500000000001</v>
       </c>
       <c r="F86">
-        <v>125.412</v>
+        <v>126.905</v>
       </c>
       <c r="G86">
         <v>8.76</v>
@@ -8321,37 +8321,37 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M86">
-        <v>29.5721496</v>
+        <v>29.924199</v>
       </c>
       <c r="N86">
-        <v>-19.00048293333334</v>
+        <v>-19.35253233333334</v>
       </c>
       <c r="O86">
-        <v>-3.800096586666668</v>
+        <v>-3.870506466666667</v>
       </c>
       <c r="P86">
-        <v>-15.20038634666667</v>
+        <v>-15.48202586666667</v>
       </c>
       <c r="Q86">
-        <v>-15.05538634666667</v>
+        <v>-15.33702586666667</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1963744762401</v>
+        <v>0.2064127746561067</v>
       </c>
       <c r="T86">
-        <v>3.095969713878654</v>
+        <v>3.302367694803898</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.07149745155263698</v>
+        <v>0.07065630506378244</v>
       </c>
       <c r="W86">
-        <v>0.2189409009238882</v>
+        <v>0.2191392432659601</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3574872577631849</v>
+        <v>0.3532815253189121</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8367,22 +8367,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2172302729744821</v>
+        <v>0.2191302729744821</v>
       </c>
       <c r="C87">
-        <v>-90.55591563458498</v>
+        <v>-92.33089733706639</v>
       </c>
       <c r="D87">
-        <v>27.58908436541502</v>
+        <v>27.30710266293361</v>
       </c>
       <c r="E87">
-        <v>38.80500000000001</v>
+        <v>40.298</v>
       </c>
       <c r="F87">
-        <v>126.905</v>
+        <v>128.398</v>
       </c>
       <c r="G87">
         <v>8.76</v>
@@ -8403,37 +8403,37 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M87">
-        <v>29.924199</v>
+        <v>30.2762484</v>
       </c>
       <c r="N87">
-        <v>-19.35253233333334</v>
+        <v>-19.70458173333333</v>
       </c>
       <c r="O87">
-        <v>-3.870506466666667</v>
+        <v>-3.940916346666667</v>
       </c>
       <c r="P87">
-        <v>-15.48202586666667</v>
+        <v>-15.76366538666667</v>
       </c>
       <c r="Q87">
-        <v>-15.33702586666667</v>
+        <v>-15.61866538666667</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2064127746561067</v>
+        <v>0.2178851157029715</v>
       </c>
       <c r="T87">
-        <v>3.302367694803898</v>
+        <v>3.538251101575605</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.07065630506378244</v>
+        <v>0.06983472012118032</v>
       </c>
       <c r="W87">
-        <v>0.2191392432659601</v>
+        <v>0.2193329729954257</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3532815253189121</v>
+        <v>0.3491736006059015</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8449,22 +8449,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2191302729744821</v>
+        <v>0.2210302729744821</v>
       </c>
       <c r="C88">
-        <v>-92.33089733706639</v>
+        <v>-94.10017321686132</v>
       </c>
       <c r="D88">
-        <v>27.30710266293361</v>
+        <v>27.0308267831387</v>
       </c>
       <c r="E88">
-        <v>40.298</v>
+        <v>41.79100000000003</v>
       </c>
       <c r="F88">
-        <v>128.398</v>
+        <v>129.891</v>
       </c>
       <c r="G88">
         <v>8.76</v>
@@ -8485,37 +8485,37 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M88">
-        <v>30.2762484</v>
+        <v>30.62829780000001</v>
       </c>
       <c r="N88">
-        <v>-19.70458173333333</v>
+        <v>-20.05663113333334</v>
       </c>
       <c r="O88">
-        <v>-3.940916346666667</v>
+        <v>-4.011326226666668</v>
       </c>
       <c r="P88">
-        <v>-15.76366538666667</v>
+        <v>-16.04530490666667</v>
       </c>
       <c r="Q88">
-        <v>-15.61866538666667</v>
+        <v>-15.90030490666667</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2178851157029715</v>
+        <v>0.2311224322955077</v>
       </c>
       <c r="T88">
-        <v>3.538251101575605</v>
+        <v>3.810424263235267</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.06983472012118032</v>
+        <v>0.06903202218875296</v>
       </c>
       <c r="W88">
-        <v>0.2193329729954257</v>
+        <v>0.2195222491678921</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3491736006059015</v>
+        <v>0.3451601109437646</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8531,22 +8531,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2210302729744821</v>
+        <v>0.2229302729744821</v>
       </c>
       <c r="C89">
-        <v>-94.10017321686132</v>
+        <v>-95.86391472300156</v>
       </c>
       <c r="D89">
-        <v>27.0308267831387</v>
+        <v>26.76008527699846</v>
       </c>
       <c r="E89">
-        <v>41.79100000000003</v>
+        <v>43.28400000000002</v>
       </c>
       <c r="F89">
-        <v>129.891</v>
+        <v>131.384</v>
       </c>
       <c r="G89">
         <v>8.76</v>
@@ -8567,37 +8567,37 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M89">
-        <v>30.62829780000001</v>
+        <v>30.9803472</v>
       </c>
       <c r="N89">
-        <v>-20.05663113333334</v>
+        <v>-20.40868053333334</v>
       </c>
       <c r="O89">
-        <v>-4.011326226666668</v>
+        <v>-4.081736106666668</v>
       </c>
       <c r="P89">
-        <v>-16.04530490666667</v>
+        <v>-16.32694442666667</v>
       </c>
       <c r="Q89">
-        <v>-15.90030490666667</v>
+        <v>-16.18194442666667</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2311224322955077</v>
+        <v>0.2465659683201334</v>
       </c>
       <c r="T89">
-        <v>3.810424263235267</v>
+        <v>4.127959618504873</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.06903202218875296</v>
+        <v>0.06824756739115349</v>
       </c>
       <c r="W89">
-        <v>0.2195222491678921</v>
+        <v>0.219707223609166</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3451601109437646</v>
+        <v>0.3412378369557674</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8613,22 +8613,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2229302729744821</v>
+        <v>0.2248302729744821</v>
       </c>
       <c r="C90">
-        <v>-95.86391472300156</v>
+        <v>-97.62228650368351</v>
       </c>
       <c r="D90">
-        <v>26.76008527699846</v>
+        <v>26.4947134963165</v>
       </c>
       <c r="E90">
-        <v>43.28400000000002</v>
+        <v>44.77700000000002</v>
       </c>
       <c r="F90">
-        <v>131.384</v>
+        <v>132.877</v>
       </c>
       <c r="G90">
         <v>8.76</v>
@@ -8649,37 +8649,37 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M90">
-        <v>30.9803472</v>
+        <v>31.3323966</v>
       </c>
       <c r="N90">
-        <v>-20.40868053333334</v>
+        <v>-20.76072993333334</v>
       </c>
       <c r="O90">
-        <v>-4.081736106666668</v>
+        <v>-4.152145986666667</v>
       </c>
       <c r="P90">
-        <v>-16.32694442666667</v>
+        <v>-16.60858394666667</v>
       </c>
       <c r="Q90">
-        <v>-16.18194442666667</v>
+        <v>-16.46358394666667</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2465659683201334</v>
+        <v>0.2648174199856001</v>
       </c>
       <c r="T90">
-        <v>4.127959618504873</v>
+        <v>4.503228674732589</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.06824756739115349</v>
+        <v>0.06748074079125289</v>
       </c>
       <c r="W90">
-        <v>0.219707223609166</v>
+        <v>0.2198880413214226</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3412378369557674</v>
+        <v>0.3374037039562644</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8695,22 +8695,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2248302729744821</v>
+        <v>0.2267302729744821</v>
       </c>
       <c r="C91">
-        <v>-97.62228650368351</v>
+        <v>-99.37544674016607</v>
       </c>
       <c r="D91">
-        <v>26.4947134963165</v>
+        <v>26.23455325983393</v>
       </c>
       <c r="E91">
-        <v>44.77700000000002</v>
+        <v>46.27000000000001</v>
       </c>
       <c r="F91">
-        <v>132.877</v>
+        <v>134.37</v>
       </c>
       <c r="G91">
         <v>8.76</v>
@@ -8731,37 +8731,37 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M91">
-        <v>31.3323966</v>
+        <v>31.684446</v>
       </c>
       <c r="N91">
-        <v>-20.76072993333334</v>
+        <v>-21.11277933333334</v>
       </c>
       <c r="O91">
-        <v>-4.152145986666667</v>
+        <v>-4.222555866666667</v>
       </c>
       <c r="P91">
-        <v>-16.60858394666667</v>
+        <v>-16.89022346666667</v>
       </c>
       <c r="Q91">
-        <v>-16.46358394666667</v>
+        <v>-16.74522346666667</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2648174199856001</v>
+        <v>0.2867191619841601</v>
       </c>
       <c r="T91">
-        <v>4.503228674732589</v>
+        <v>4.953551542205847</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.06748074079125289</v>
+        <v>0.0667309547824612</v>
       </c>
       <c r="W91">
-        <v>0.2198880413214226</v>
+        <v>0.2200648408622957</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3374037039562644</v>
+        <v>0.3336547739123059</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8777,22 +8777,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2267302729744821</v>
+        <v>0.2286302729744821</v>
       </c>
       <c r="C92">
-        <v>-99.37544674016607</v>
+        <v>-101.1235474611882</v>
       </c>
       <c r="D92">
-        <v>26.23455325983393</v>
+        <v>25.9794525388118</v>
       </c>
       <c r="E92">
-        <v>46.27000000000001</v>
+        <v>47.76300000000003</v>
       </c>
       <c r="F92">
-        <v>134.37</v>
+        <v>135.863</v>
       </c>
       <c r="G92">
         <v>8.76</v>
@@ -8813,37 +8813,37 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M92">
-        <v>31.684446</v>
+        <v>32.03649540000001</v>
       </c>
       <c r="N92">
-        <v>-21.11277933333334</v>
+        <v>-21.46482873333334</v>
       </c>
       <c r="O92">
-        <v>-4.222555866666667</v>
+        <v>-4.292965746666669</v>
       </c>
       <c r="P92">
-        <v>-16.89022346666667</v>
+        <v>-17.17186298666667</v>
       </c>
       <c r="Q92">
-        <v>-16.74522346666667</v>
+        <v>-17.02686298666667</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2867191619841601</v>
+        <v>0.313487957760178</v>
       </c>
       <c r="T92">
-        <v>4.953551542205847</v>
+        <v>5.503946158006499</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.0667309547824612</v>
+        <v>0.06599764758704951</v>
       </c>
       <c r="W92">
-        <v>0.2200648408622957</v>
+        <v>0.2202377546989737</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3336547739123059</v>
+        <v>0.3299882379352476</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8859,22 +8859,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2286302729744821</v>
+        <v>0.2305302729744821</v>
       </c>
       <c r="C93">
-        <v>-101.1235474611882</v>
+        <v>-102.8667348392189</v>
       </c>
       <c r="D93">
-        <v>25.9794525388118</v>
+        <v>25.72926516078108</v>
       </c>
       <c r="E93">
-        <v>47.76300000000003</v>
+        <v>49.25600000000003</v>
       </c>
       <c r="F93">
-        <v>135.863</v>
+        <v>137.356</v>
       </c>
       <c r="G93">
         <v>8.76</v>
@@ -8895,37 +8895,37 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M93">
-        <v>32.03649540000001</v>
+        <v>32.38854480000001</v>
       </c>
       <c r="N93">
-        <v>-21.46482873333334</v>
+        <v>-21.81687813333334</v>
       </c>
       <c r="O93">
-        <v>-4.292965746666669</v>
+        <v>-4.363375626666668</v>
       </c>
       <c r="P93">
-        <v>-17.17186298666667</v>
+        <v>-17.45350250666667</v>
       </c>
       <c r="Q93">
-        <v>-17.02686298666667</v>
+        <v>-17.30850250666667</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.313487957760178</v>
+        <v>0.3469489524802002</v>
       </c>
       <c r="T93">
-        <v>5.503946158006499</v>
+        <v>6.191939427757312</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.06599764758704951</v>
+        <v>0.06528028185240768</v>
       </c>
       <c r="W93">
-        <v>0.2202377546989737</v>
+        <v>0.2204069095392023</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3299882379352476</v>
+        <v>0.3264014092620383</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8941,22 +8941,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2305302729744821</v>
+        <v>0.2324302729744821</v>
       </c>
       <c r="C94">
-        <v>-102.8667348392189</v>
+        <v>-104.605149469753</v>
       </c>
       <c r="D94">
-        <v>25.72926516078108</v>
+        <v>25.48385053024703</v>
       </c>
       <c r="E94">
-        <v>49.25600000000003</v>
+        <v>50.74900000000002</v>
       </c>
       <c r="F94">
-        <v>137.356</v>
+        <v>138.849</v>
       </c>
       <c r="G94">
         <v>8.76</v>
@@ -8977,37 +8977,37 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M94">
-        <v>32.38854480000001</v>
+        <v>32.7405942</v>
       </c>
       <c r="N94">
-        <v>-21.81687813333334</v>
+        <v>-22.16892753333334</v>
       </c>
       <c r="O94">
-        <v>-4.363375626666668</v>
+        <v>-4.433785506666668</v>
       </c>
       <c r="P94">
-        <v>-17.45350250666667</v>
+        <v>-17.73514202666667</v>
       </c>
       <c r="Q94">
-        <v>-17.30850250666667</v>
+        <v>-17.59014202666667</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3469489524802002</v>
+        <v>0.3899702314059432</v>
       </c>
       <c r="T94">
-        <v>6.191939427757312</v>
+        <v>7.076502203151214</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.06528028185240768</v>
+        <v>0.06457834333786566</v>
       </c>
       <c r="W94">
-        <v>0.2204069095392023</v>
+        <v>0.2205724266409313</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3264014092620383</v>
+        <v>0.3228917166893283</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9023,22 +9023,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2324302729744821</v>
+        <v>0.2343302729744821</v>
       </c>
       <c r="C95">
-        <v>-104.605149469753</v>
+        <v>-106.3389266347733</v>
       </c>
       <c r="D95">
-        <v>25.48385053024703</v>
+        <v>25.24307336522667</v>
       </c>
       <c r="E95">
-        <v>50.74900000000002</v>
+        <v>52.24200000000002</v>
       </c>
       <c r="F95">
-        <v>138.849</v>
+        <v>140.342</v>
       </c>
       <c r="G95">
         <v>8.76</v>
@@ -9059,37 +9059,37 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M95">
-        <v>32.7405942</v>
+        <v>33.0926436</v>
       </c>
       <c r="N95">
-        <v>-22.16892753333334</v>
+        <v>-22.52097693333334</v>
       </c>
       <c r="O95">
-        <v>-4.433785506666668</v>
+        <v>-4.504195386666668</v>
       </c>
       <c r="P95">
-        <v>-17.73514202666667</v>
+        <v>-18.01678154666667</v>
       </c>
       <c r="Q95">
-        <v>-17.59014202666667</v>
+        <v>-17.87178154666667</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3899702314059432</v>
+        <v>0.4473319366402672</v>
       </c>
       <c r="T95">
-        <v>7.076502203151214</v>
+        <v>8.255919237009753</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.06457834333786566</v>
+        <v>0.06389133968533518</v>
       </c>
       <c r="W95">
-        <v>0.2205724266409313</v>
+        <v>0.220734422102198</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3228917166893283</v>
+        <v>0.3194566984266759</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9105,22 +9105,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2343302729744821</v>
+        <v>0.2362302729744821</v>
       </c>
       <c r="C96">
-        <v>-106.3389266347733</v>
+        <v>-108.0681965514182</v>
       </c>
       <c r="D96">
-        <v>25.24307336522667</v>
+        <v>25.00680344858179</v>
       </c>
       <c r="E96">
-        <v>52.24200000000002</v>
+        <v>53.73500000000001</v>
       </c>
       <c r="F96">
-        <v>140.342</v>
+        <v>141.835</v>
       </c>
       <c r="G96">
         <v>8.76</v>
@@ -9141,37 +9141,37 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M96">
-        <v>33.0926436</v>
+        <v>33.444693</v>
       </c>
       <c r="N96">
-        <v>-22.52097693333334</v>
+        <v>-22.87302633333334</v>
       </c>
       <c r="O96">
-        <v>-4.504195386666668</v>
+        <v>-4.574605266666667</v>
       </c>
       <c r="P96">
-        <v>-18.01678154666667</v>
+        <v>-18.29842106666667</v>
       </c>
       <c r="Q96">
-        <v>-17.87178154666667</v>
+        <v>-18.15342106666667</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4473319366402672</v>
+        <v>0.5276383239683209</v>
       </c>
       <c r="T96">
-        <v>8.255919237009753</v>
+        <v>9.907103084411709</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.06389133968533518</v>
+        <v>0.06321879926759481</v>
       </c>
       <c r="W96">
-        <v>0.220734422102198</v>
+        <v>0.2208930071327012</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3194566984266759</v>
+        <v>0.316093996337974</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9187,22 +9187,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2362302729744821</v>
+        <v>0.2381302729744821</v>
       </c>
       <c r="C97">
-        <v>-108.0681965514182</v>
+        <v>-109.7930846068123</v>
       </c>
       <c r="D97">
-        <v>25.00680344858179</v>
+        <v>24.77491539318776</v>
       </c>
       <c r="E97">
-        <v>53.73500000000001</v>
+        <v>55.22800000000004</v>
       </c>
       <c r="F97">
-        <v>141.835</v>
+        <v>143.328</v>
       </c>
       <c r="G97">
         <v>8.76</v>
@@ -9223,37 +9223,37 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M97">
-        <v>33.444693</v>
+        <v>33.79674240000001</v>
       </c>
       <c r="N97">
-        <v>-22.87302633333334</v>
+        <v>-23.22507573333334</v>
       </c>
       <c r="O97">
-        <v>-4.574605266666667</v>
+        <v>-4.645015146666668</v>
       </c>
       <c r="P97">
-        <v>-18.29842106666667</v>
+        <v>-18.58006058666667</v>
       </c>
       <c r="Q97">
-        <v>-18.15342106666667</v>
+        <v>-18.43506058666667</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5276383239683209</v>
+        <v>0.6480979049604012</v>
       </c>
       <c r="T97">
-        <v>9.907103084411709</v>
+        <v>12.38387885551464</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.06321879926759481</v>
+        <v>0.06256027010855736</v>
       </c>
       <c r="W97">
-        <v>0.2208930071327012</v>
+        <v>0.2210482883084022</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9261,7 +9261,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.316093996337974</v>
+        <v>0.3128013505427867</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9269,22 +9269,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2381302729744821</v>
+        <v>0.2400302729744821</v>
       </c>
       <c r="C98">
-        <v>-109.7930846068123</v>
+        <v>-111.5137115799528</v>
       </c>
       <c r="D98">
-        <v>24.77491539318773</v>
+        <v>24.54728842004717</v>
       </c>
       <c r="E98">
-        <v>55.22800000000001</v>
+        <v>56.721</v>
       </c>
       <c r="F98">
-        <v>143.328</v>
+        <v>144.821</v>
       </c>
       <c r="G98">
         <v>8.76</v>
@@ -9305,37 +9305,37 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M98">
-        <v>33.7967424</v>
+        <v>34.1487918</v>
       </c>
       <c r="N98">
-        <v>-23.22507573333333</v>
+        <v>-23.57712513333333</v>
       </c>
       <c r="O98">
-        <v>-4.645015146666667</v>
+        <v>-4.715425026666667</v>
       </c>
       <c r="P98">
-        <v>-18.58006058666667</v>
+        <v>-18.86170010666667</v>
       </c>
       <c r="Q98">
-        <v>-18.43506058666667</v>
+        <v>-18.71670010666667</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6480979049603997</v>
+        <v>0.8488638732805329</v>
       </c>
       <c r="T98">
-        <v>12.38387885551461</v>
+        <v>16.51183847401948</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.06256027010855737</v>
+        <v>0.06191531887032482</v>
       </c>
       <c r="W98">
-        <v>0.2210482883084022</v>
+        <v>0.2212003678103774</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3128013505427868</v>
+        <v>0.3095765943516241</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9351,22 +9351,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2400302729744821</v>
+        <v>0.2419302729744821</v>
       </c>
       <c r="C99">
-        <v>-111.5137115799528</v>
+        <v>-113.2301938514753</v>
       </c>
       <c r="D99">
-        <v>24.54728842004717</v>
+        <v>24.32380614852469</v>
       </c>
       <c r="E99">
-        <v>56.721</v>
+        <v>58.21400000000003</v>
       </c>
       <c r="F99">
-        <v>144.821</v>
+        <v>146.314</v>
       </c>
       <c r="G99">
         <v>8.76</v>
@@ -9387,37 +9387,37 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M99">
-        <v>34.1487918</v>
+        <v>34.5008412</v>
       </c>
       <c r="N99">
-        <v>-23.57712513333333</v>
+        <v>-23.92917453333334</v>
       </c>
       <c r="O99">
-        <v>-4.715425026666667</v>
+        <v>-4.785834906666667</v>
       </c>
       <c r="P99">
-        <v>-18.86170010666667</v>
+        <v>-19.14333962666667</v>
       </c>
       <c r="Q99">
-        <v>-18.71670010666667</v>
+        <v>-18.99833962666667</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.8488638732805329</v>
+        <v>1.250395809920799</v>
       </c>
       <c r="T99">
-        <v>16.51183847401948</v>
+        <v>24.76775771102922</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.06191531887032482</v>
+        <v>0.06128352990226027</v>
       </c>
       <c r="W99">
-        <v>0.2212003678103774</v>
+        <v>0.221349343649047</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3095765943516241</v>
+        <v>0.3064176495113013</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9433,22 +9433,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2419302729744821</v>
+        <v>0.2438302729744821</v>
       </c>
       <c r="C100">
-        <v>-113.2301938514753</v>
+        <v>-114.9426436020636</v>
       </c>
       <c r="D100">
-        <v>24.32380614852469</v>
+        <v>24.10435639793641</v>
       </c>
       <c r="E100">
-        <v>58.21400000000003</v>
+        <v>59.70700000000002</v>
       </c>
       <c r="F100">
-        <v>146.314</v>
+        <v>147.807</v>
       </c>
       <c r="G100">
         <v>8.76</v>
@@ -9469,37 +9469,37 @@
         <v>10.57166666666667</v>
       </c>
       <c r="M100">
-        <v>34.5008412</v>
+        <v>34.8528906</v>
       </c>
       <c r="N100">
-        <v>-23.92917453333334</v>
+        <v>-24.28122393333334</v>
       </c>
       <c r="O100">
-        <v>-4.785834906666667</v>
+        <v>-4.856244786666668</v>
       </c>
       <c r="P100">
-        <v>-19.14333962666667</v>
+        <v>-19.42497914666667</v>
       </c>
       <c r="Q100">
-        <v>-18.99833962666667</v>
+        <v>-19.27997914666667</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.250395809920799</v>
+        <v>2.454991619841599</v>
       </c>
       <c r="T100">
-        <v>24.76775771102922</v>
+        <v>49.53551542205843</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.06128352990226027</v>
+        <v>0.06066450434769199</v>
       </c>
       <c r="W100">
-        <v>0.221349343649047</v>
+        <v>0.2214953098748143</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9507,91 +9507,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3064176495113013</v>
+        <v>0.3033225217384599</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2438302729744821</v>
-      </c>
-      <c r="C101">
-        <v>-114.9426436020636</v>
-      </c>
-      <c r="D101">
-        <v>24.10435639793641</v>
-      </c>
-      <c r="E101">
-        <v>59.70700000000002</v>
-      </c>
-      <c r="F101">
-        <v>147.807</v>
-      </c>
-      <c r="G101">
-        <v>8.76</v>
-      </c>
-      <c r="H101">
-        <v>61.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>10.71666666666667</v>
-      </c>
-      <c r="K101">
-        <v>0.145</v>
-      </c>
-      <c r="L101">
-        <v>10.57166666666667</v>
-      </c>
-      <c r="M101">
-        <v>34.8528906</v>
-      </c>
-      <c r="N101">
-        <v>-24.28122393333334</v>
-      </c>
-      <c r="O101">
-        <v>-4.856244786666668</v>
-      </c>
-      <c r="P101">
-        <v>-19.42497914666667</v>
-      </c>
-      <c r="Q101">
-        <v>-19.27997914666667</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.454991619841599</v>
-      </c>
-      <c r="T101">
-        <v>49.53551542205843</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06066450434769199</v>
-      </c>
-      <c r="W101">
-        <v>0.2214953098748143</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3033225217384599</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
